--- a/144F20/Topic 5/Histogram-BarChart.xlsx
+++ b/144F20/Topic 5/Histogram-BarChart.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail-my.sharepoint.com/personal/richard_ketchersid_gcu_edu/Documents/Course Materials/144/Excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail-my.sharepoint.com/personal/richard_ketchersid_gcu_edu/Documents/Course Materials/git/Teaching/144F20/Topic 5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="575" documentId="13_ncr:1_{3CBBB4A1-34B7-4D45-A485-52FE9F5BFF1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB5E87DE-AABF-4B23-B81B-03655C1B4BF9}"/>
+  <xr:revisionPtr revIDLastSave="590" documentId="13_ncr:1_{3CBBB4A1-34B7-4D45-A485-52FE9F5BFF1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69B13D88-97CE-4252-BE0B-6FE9E52CE96A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B9F88BC-F133-4FE5-9223-57343937B704}"/>
   </bookViews>
@@ -246,7 +246,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -314,6 +314,22 @@
     <font>
       <b/>
       <sz val="14"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -720,7 +736,7 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -911,6 +927,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1123,16 +1157,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>88</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18</c:v>
+                  <c:v>74</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>21</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>68</c:v>
+                  <c:v>58</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1273,6 +1307,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1280,7 +1315,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1493,16 +1527,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>18</c:v>
+                  <c:v>74</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>21</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>68</c:v>
+                  <c:v>58</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>88</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1643,6 +1677,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1650,7 +1685,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1808,370 +1842,370 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="134"/>
                 <c:pt idx="0">
-                  <c:v>69.475439609415915</c:v>
+                  <c:v>66.242934483345223</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>63.616852833726099</c:v>
+                  <c:v>64.733945362871481</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>65.991284820702205</c:v>
+                  <c:v>66.20535912179669</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>66.623824883313574</c:v>
+                  <c:v>70.566312528836036</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>67.230278665089998</c:v>
+                  <c:v>63.835344305202476</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>67.918580042523629</c:v>
+                  <c:v>68.12539793235554</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>66.23931331263168</c:v>
+                  <c:v>70.406940346506488</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>66.714785283063534</c:v>
+                  <c:v>68.758300257521469</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>62.717326388430067</c:v>
+                  <c:v>68.052733629157672</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>72.886580462744575</c:v>
+                  <c:v>60.337737144125832</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>63.360895965013576</c:v>
+                  <c:v>66.232521294311383</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>70.966145710318912</c:v>
+                  <c:v>66.244666483025384</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>66.463157399011621</c:v>
+                  <c:v>72.926828735755066</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>71.375758875760511</c:v>
+                  <c:v>70.680988386002909</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>63.376406097747228</c:v>
+                  <c:v>62.879952427261607</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>68.993907295192471</c:v>
+                  <c:v>66.520814865113479</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>65.121698245632544</c:v>
+                  <c:v>65.799904367928704</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>67.566494777888394</c:v>
+                  <c:v>63.813916334643544</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>69.580088601349573</c:v>
+                  <c:v>64.136402301466291</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>62.798699462229642</c:v>
+                  <c:v>62.786435009059964</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>61.272925749941827</c:v>
+                  <c:v>69.568648923401881</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>68.196609272025015</c:v>
+                  <c:v>64.317414586693502</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>63.607069756577225</c:v>
+                  <c:v>66.061558501820087</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>66.366132304135633</c:v>
+                  <c:v>65.765903101851904</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>68.751086314844912</c:v>
+                  <c:v>66.820491715120312</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>65.873687668860754</c:v>
+                  <c:v>68.263157362157685</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>69.038928403175078</c:v>
+                  <c:v>63.751664011456583</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>64.79447986422656</c:v>
+                  <c:v>61.139526115604589</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>68.258326414238397</c:v>
+                  <c:v>61.832624825508717</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>62.730611908912472</c:v>
+                  <c:v>64.458155759942073</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>67.732790768257743</c:v>
+                  <c:v>71.43623843106856</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>67.732008088296539</c:v>
+                  <c:v>70.380261068021241</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>66.933572867587372</c:v>
+                  <c:v>67.958562513892531</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>68.250670132527418</c:v>
+                  <c:v>67.050559490969547</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>59.661817353543697</c:v>
+                  <c:v>67.724337352905977</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>60.09508594830038</c:v>
+                  <c:v>62.770845880537131</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>70.787846692610145</c:v>
+                  <c:v>62.293042269721461</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>69.66281205015099</c:v>
+                  <c:v>65.536563806302993</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>69.01873232943548</c:v>
+                  <c:v>67.207745864465835</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>72.904379406546724</c:v>
+                  <c:v>62.547370272693669</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>66.741820053561838</c:v>
+                  <c:v>69.392140184375819</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>65.407956382634339</c:v>
+                  <c:v>67.729854637108858</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>67.248773020074722</c:v>
+                  <c:v>66.083867300281312</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>63.616341912223312</c:v>
+                  <c:v>67.317733735635542</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>66.016419424342288</c:v>
+                  <c:v>66.770176536641756</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>69.57620562002127</c:v>
+                  <c:v>65.802601715232484</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>65.660848371674192</c:v>
+                  <c:v>60.686868681992188</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>62.368526769562038</c:v>
+                  <c:v>70.631436966120845</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>63.234695801963049</c:v>
+                  <c:v>67.822231309414491</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>69.877266762241959</c:v>
+                  <c:v>65.451083517140262</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>68.614950776555119</c:v>
+                  <c:v>69.889156638810135</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>60.223604529459777</c:v>
+                  <c:v>62.575792941732757</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>70.803936966712754</c:v>
+                  <c:v>68.790168500099284</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>65.406153874396821</c:v>
+                  <c:v>65.195396415878776</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>62.478361733531543</c:v>
+                  <c:v>67.083526236133267</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>65.733687038141014</c:v>
+                  <c:v>69.226471004443937</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>61.344876881641696</c:v>
+                  <c:v>61.030827750936695</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>66.240712540221054</c:v>
+                  <c:v>63.986155098356939</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>64.539003450063646</c:v>
+                  <c:v>63.699223418430471</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>64.106198254993345</c:v>
+                  <c:v>60.524657455882306</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>66.309521273648855</c:v>
+                  <c:v>63.690036126164046</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>62.523738128542149</c:v>
+                  <c:v>68.393102668615157</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>69.687286369623536</c:v>
+                  <c:v>72.965816474382478</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>61.730907352530977</c:v>
+                  <c:v>69.132891507536783</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>61.341755030029134</c:v>
+                  <c:v>64.560732642842893</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>69.65492612657728</c:v>
+                  <c:v>65.06553956316084</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>69.561719211726725</c:v>
+                  <c:v>67.584435173268702</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>65.511879244613937</c:v>
+                  <c:v>63.388505838246573</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>63.400143040605201</c:v>
+                  <c:v>68.826396011148987</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>68.935900027782765</c:v>
+                  <c:v>66.901953310334136</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>58.274445673974355</c:v>
+                  <c:v>66.847864430089132</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>65.875412947247852</c:v>
+                  <c:v>63.959480931125611</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>68.3712034609309</c:v>
+                  <c:v>67.00248895781742</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>67.790685459937805</c:v>
+                  <c:v>61.846276541973559</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>67.193867540338374</c:v>
+                  <c:v>68.749918497984808</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>63.511825680366904</c:v>
+                  <c:v>67.412689056446894</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>67.699207332452957</c:v>
+                  <c:v>68.295978068811891</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>66.491354103346495</c:v>
+                  <c:v>63.508756989083238</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>67.422302083424213</c:v>
+                  <c:v>61.360217869183117</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>71.851338202611345</c:v>
+                  <c:v>70.181761015750197</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>68.52922467858356</c:v>
+                  <c:v>67.717765900309033</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>63.337405874236993</c:v>
+                  <c:v>66.949422645155238</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>65.34458773689299</c:v>
+                  <c:v>67.580467316864755</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>64.235810639210456</c:v>
+                  <c:v>65.615480189559364</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>69.085570337652257</c:v>
+                  <c:v>64.663874146530233</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>64.501702664742027</c:v>
+                  <c:v>63.554668904705267</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>64.023955392929409</c:v>
+                  <c:v>64.212661108492156</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>67.78337711608296</c:v>
+                  <c:v>63.582420345152578</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>64.917425313046166</c:v>
+                  <c:v>62.866769667379245</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>62.31059437379664</c:v>
+                  <c:v>69.763586669985443</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>67.029092748141395</c:v>
+                  <c:v>66.019920085971251</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>65.152264894695918</c:v>
+                  <c:v>68.577897562400949</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>61.199775990691577</c:v>
+                  <c:v>62.928766757172859</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>67.262455224716504</c:v>
+                  <c:v>60.650378600522203</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>64.354946312367261</c:v>
+                  <c:v>62.55492046456169</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>63.219410471693351</c:v>
+                  <c:v>64.339837049717559</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>65.831785088530282</c:v>
+                  <c:v>64.601510691071496</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>66.197320849148809</c:v>
+                  <c:v>69.18219008879332</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>62.884291193572345</c:v>
+                  <c:v>65.18081678544219</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>63.460679233636078</c:v>
+                  <c:v>62.53000958906641</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>73.396319499285866</c:v>
+                  <c:v>67.023429216239364</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>69.092637651587808</c:v>
+                  <c:v>65.419694574125401</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>64.589616250500043</c:v>
+                  <c:v>64.527943122945032</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>68.946282091601773</c:v>
+                  <c:v>63.990051817670349</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>65.383162698307871</c:v>
+                  <c:v>64.048047928929293</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>70.301066217215109</c:v>
+                  <c:v>66.004054158487477</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>70.203168423284751</c:v>
+                  <c:v>63.730839164069721</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>71.809462331261898</c:v>
+                  <c:v>64.306882565104132</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>73.447719531860685</c:v>
+                  <c:v>65.939897352211545</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>68.717819107289174</c:v>
+                  <c:v>64.462662881571831</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>72.504274540477724</c:v>
+                  <c:v>68.607508675355433</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>69.951422067288604</c:v>
+                  <c:v>64.862267423302882</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>58.303169578667131</c:v>
+                  <c:v>65.029873080459183</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>66.480416186446703</c:v>
+                  <c:v>60.474622861672934</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>68.577242095825738</c:v>
+                  <c:v>66.903253566519751</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>65.552419774222798</c:v>
+                  <c:v>61.708456177973119</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>63.471827882930448</c:v>
+                  <c:v>64.37725790007093</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>63.740992429480627</c:v>
+                  <c:v>68.591284302048706</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>61.109774491819493</c:v>
+                  <c:v>70.403276438005832</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>71.67991871011391</c:v>
+                  <c:v>62.94308564332897</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>68.559326478881999</c:v>
+                  <c:v>65.928881334843581</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>71.443183406472144</c:v>
+                  <c:v>62.630583080097253</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2704,6 +2738,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2711,7 +2746,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2933,34 +2967,34 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>59.087222836987181</c:v>
+                  <c:v>60.968868572062917</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60.7</c:v>
+                  <c:v>62.249999999999993</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>62.3</c:v>
+                  <c:v>63.54999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>63.900000000000006</c:v>
+                  <c:v>64.849999999999994</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>65.5</c:v>
+                  <c:v>66.149999999999977</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>67.099999999999994</c:v>
+                  <c:v>67.449999999999989</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>68.699999999999989</c:v>
+                  <c:v>68.749999999999972</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>70.299999999999983</c:v>
+                  <c:v>70.049999999999983</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>71.899999999999977</c:v>
+                  <c:v>71.349999999999966</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>73.499999999999972</c:v>
+                  <c:v>72.649999999999977</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2972,34 +3006,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>3</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>20</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>21</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>19</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>13</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3135,6 +3169,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3142,7 +3177,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3363,34 +3397,34 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>59.087222836987181</c:v>
+                  <c:v>60.968868572062917</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60.7</c:v>
+                  <c:v>62.249999999999993</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>62.3</c:v>
+                  <c:v>63.54999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>63.900000000000006</c:v>
+                  <c:v>64.849999999999994</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>65.5</c:v>
+                  <c:v>66.149999999999977</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>67.099999999999994</c:v>
+                  <c:v>67.449999999999989</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>68.699999999999989</c:v>
+                  <c:v>68.749999999999972</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>70.299999999999983</c:v>
+                  <c:v>70.049999999999983</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>71.899999999999977</c:v>
+                  <c:v>71.349999999999966</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>73.499999999999972</c:v>
+                  <c:v>72.649999999999977</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3402,34 +3436,34 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>2.4590163934426229E-2</c:v>
+                  <c:v>6.5573770491803282E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.737704918032787E-2</c:v>
+                  <c:v>0.10655737704918032</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.3770491803278687E-2</c:v>
+                  <c:v>0.13934426229508196</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>0.15573770491803279</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.13934426229508196</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>0.16393442622950818</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.16393442622950818</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.1721311475409836</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.15573770491803279</c:v>
+                  <c:v>0.12295081967213115</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.10655737704918032</c:v>
+                  <c:v>8.1967213114754092E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.9180327868852458E-2</c:v>
+                  <c:v>8.1967213114754103E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.2786885245901641E-2</c:v>
+                  <c:v>1.6393442622950821E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3565,6 +3599,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3572,7 +3607,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3770,34 +3804,34 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>59.087222836987181</c:v>
+                  <c:v>60.968868572062917</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60.7</c:v>
+                  <c:v>62.249999999999993</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>62.3</c:v>
+                  <c:v>63.54999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>63.900000000000006</c:v>
+                  <c:v>64.849999999999994</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>65.5</c:v>
+                  <c:v>66.149999999999977</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>67.099999999999994</c:v>
+                  <c:v>67.449999999999989</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>68.699999999999989</c:v>
+                  <c:v>68.749999999999972</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>70.299999999999983</c:v>
+                  <c:v>70.049999999999983</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>71.899999999999977</c:v>
+                  <c:v>71.349999999999966</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>73.499999999999972</c:v>
+                  <c:v>72.649999999999977</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3809,34 +3843,34 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.88</c:v>
+                  <c:v>6.15</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.38</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.63</c:v>
+                  <c:v>13.08</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12.5</c:v>
+                  <c:v>14.62</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>12.5</c:v>
+                  <c:v>13.08</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>13.13</c:v>
+                  <c:v>15.38</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>11.88</c:v>
+                  <c:v>11.54</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.1300000000000008</c:v>
+                  <c:v>7.69</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.75</c:v>
+                  <c:v>0.77</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.5</c:v>
+                  <c:v>1.54</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3972,6 +4006,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3979,7 +4014,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4176,34 +4210,34 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>59.087222836987181</c:v>
+                  <c:v>60.968868572062917</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60.7</c:v>
+                  <c:v>62.249999999999993</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>62.3</c:v>
+                  <c:v>63.54999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>63.900000000000006</c:v>
+                  <c:v>64.849999999999994</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>65.5</c:v>
+                  <c:v>66.149999999999977</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>67.099999999999994</c:v>
+                  <c:v>67.449999999999989</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>68.699999999999989</c:v>
+                  <c:v>68.749999999999972</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>70.299999999999983</c:v>
+                  <c:v>70.049999999999983</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>71.899999999999977</c:v>
+                  <c:v>71.349999999999966</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>73.499999999999972</c:v>
+                  <c:v>72.649999999999977</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4215,34 +4249,34 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1.540983606557377E-2</c:v>
+                  <c:v>5.0409836065573775E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.5901639344262291E-2</c:v>
+                  <c:v>8.1967213114754092E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.6147540983606558E-2</c:v>
+                  <c:v>0.10721311475409837</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.10245901639344263</c:v>
+                  <c:v>0.11983606557377048</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.10245901639344263</c:v>
+                  <c:v>0.10721311475409837</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.10762295081967213</c:v>
+                  <c:v>0.12606557377049182</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>9.7377049180327871E-2</c:v>
+                  <c:v>9.4590163934426222E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.6639344262295092E-2</c:v>
+                  <c:v>6.3032786885245912E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.0737704918032786E-2</c:v>
+                  <c:v>6.3114754098360657E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.0491803278688523E-2</c:v>
+                  <c:v>1.2622950819672131E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4378,6 +4412,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4385,7 +4420,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4642,64 +4676,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>58.3</c:v>
+                  <c:v>60.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>58.3</c:v>
+                  <c:v>60.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>60.7</c:v>
+                  <c:v>62.249999999999993</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>63.1</c:v>
+                  <c:v>64.199999999999989</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>63.1</c:v>
+                  <c:v>64.199999999999989</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>63.1</c:v>
+                  <c:v>64.199999999999989</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>63.1</c:v>
+                  <c:v>64.199999999999989</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>64.7</c:v>
+                  <c:v>65.499999999999986</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>66.3</c:v>
+                  <c:v>66.799999999999983</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>66.3</c:v>
+                  <c:v>66.799999999999983</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>66.3</c:v>
+                  <c:v>66.799999999999983</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>66.3</c:v>
+                  <c:v>66.799999999999983</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>67.899999999999991</c:v>
+                  <c:v>68.09999999999998</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>69.499999999999986</c:v>
+                  <c:v>69.399999999999977</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>69.499999999999986</c:v>
+                  <c:v>69.399999999999977</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>69.499999999999986</c:v>
+                  <c:v>69.399999999999977</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>69.499999999999986</c:v>
+                  <c:v>69.399999999999977</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>71.899999999999977</c:v>
+                  <c:v>71.349999999999966</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>74.299999999999969</c:v>
+                  <c:v>73.299999999999969</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>74.299999999999969</c:v>
+                  <c:v>73.299999999999969</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4714,13 +4748,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.9583333333333299</c:v>
+                  <c:v>9.743589743589764</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.9583333333333299</c:v>
+                  <c:v>9.743589743589764</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.9583333333333299</c:v>
+                  <c:v>9.743589743589764</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -4729,13 +4763,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>12.500000000000016</c:v>
+                  <c:v>13.846153846153877</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>12.500000000000016</c:v>
+                  <c:v>13.846153846153877</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>12.500000000000016</c:v>
+                  <c:v>13.846153846153877</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -4744,13 +4778,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12.500000000000044</c:v>
+                  <c:v>13.46153846153849</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>12.500000000000044</c:v>
+                  <c:v>13.46153846153849</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>12.500000000000044</c:v>
+                  <c:v>13.46153846153849</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0</c:v>
@@ -4759,13 +4793,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.7916666666666838</c:v>
+                  <c:v>3.3333333333333406</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4.7916666666666838</c:v>
+                  <c:v>3.3333333333333406</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.7916666666666838</c:v>
+                  <c:v>3.3333333333333406</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0</c:v>
@@ -4810,370 +4844,370 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="122"/>
                 <c:pt idx="0">
-                  <c:v>69.475439609415915</c:v>
+                  <c:v>66.242934483345223</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>63.616852833726099</c:v>
+                  <c:v>64.733945362871481</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>65.991284820702205</c:v>
+                  <c:v>66.20535912179669</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>66.623824883313574</c:v>
+                  <c:v>70.566312528836036</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>67.230278665089998</c:v>
+                  <c:v>63.835344305202476</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>67.918580042523629</c:v>
+                  <c:v>68.12539793235554</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>66.23931331263168</c:v>
+                  <c:v>70.406940346506488</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>66.714785283063534</c:v>
+                  <c:v>68.758300257521469</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>62.717326388430067</c:v>
+                  <c:v>68.052733629157672</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>72.886580462744575</c:v>
+                  <c:v>60.337737144125832</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>63.360895965013576</c:v>
+                  <c:v>66.232521294311383</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>70.966145710318912</c:v>
+                  <c:v>66.244666483025384</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>66.463157399011621</c:v>
+                  <c:v>72.926828735755066</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>71.375758875760511</c:v>
+                  <c:v>70.680988386002909</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>63.376406097747228</c:v>
+                  <c:v>62.879952427261607</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>68.993907295192471</c:v>
+                  <c:v>66.520814865113479</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>65.121698245632544</c:v>
+                  <c:v>65.799904367928704</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>67.566494777888394</c:v>
+                  <c:v>63.813916334643544</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>69.580088601349573</c:v>
+                  <c:v>64.136402301466291</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>62.798699462229642</c:v>
+                  <c:v>62.786435009059964</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>61.272925749941827</c:v>
+                  <c:v>69.568648923401881</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>68.196609272025015</c:v>
+                  <c:v>64.317414586693502</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>63.607069756577225</c:v>
+                  <c:v>66.061558501820087</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>66.366132304135633</c:v>
+                  <c:v>65.765903101851904</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>68.751086314844912</c:v>
+                  <c:v>66.820491715120312</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>65.873687668860754</c:v>
+                  <c:v>68.263157362157685</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>69.038928403175078</c:v>
+                  <c:v>63.751664011456583</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>64.79447986422656</c:v>
+                  <c:v>61.139526115604589</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>68.258326414238397</c:v>
+                  <c:v>61.832624825508717</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>62.730611908912472</c:v>
+                  <c:v>64.458155759942073</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>67.732790768257743</c:v>
+                  <c:v>71.43623843106856</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>67.732008088296539</c:v>
+                  <c:v>70.380261068021241</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>66.933572867587372</c:v>
+                  <c:v>67.958562513892531</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>68.250670132527418</c:v>
+                  <c:v>67.050559490969547</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>59.661817353543697</c:v>
+                  <c:v>67.724337352905977</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>60.09508594830038</c:v>
+                  <c:v>62.770845880537131</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>70.787846692610145</c:v>
+                  <c:v>62.293042269721461</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>69.66281205015099</c:v>
+                  <c:v>65.536563806302993</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>69.01873232943548</c:v>
+                  <c:v>67.207745864465835</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>72.904379406546724</c:v>
+                  <c:v>62.547370272693669</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>66.741820053561838</c:v>
+                  <c:v>69.392140184375819</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>65.407956382634339</c:v>
+                  <c:v>67.729854637108858</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>67.248773020074722</c:v>
+                  <c:v>66.083867300281312</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>63.616341912223312</c:v>
+                  <c:v>67.317733735635542</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>66.016419424342288</c:v>
+                  <c:v>66.770176536641756</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>69.57620562002127</c:v>
+                  <c:v>65.802601715232484</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>65.660848371674192</c:v>
+                  <c:v>60.686868681992188</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>62.368526769562038</c:v>
+                  <c:v>70.631436966120845</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>63.234695801963049</c:v>
+                  <c:v>67.822231309414491</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>69.877266762241959</c:v>
+                  <c:v>65.451083517140262</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>68.614950776555119</c:v>
+                  <c:v>69.889156638810135</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>60.223604529459777</c:v>
+                  <c:v>62.575792941732757</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>70.803936966712754</c:v>
+                  <c:v>68.790168500099284</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>65.406153874396821</c:v>
+                  <c:v>65.195396415878776</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>62.478361733531543</c:v>
+                  <c:v>67.083526236133267</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>65.733687038141014</c:v>
+                  <c:v>69.226471004443937</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>61.344876881641696</c:v>
+                  <c:v>61.030827750936695</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>66.240712540221054</c:v>
+                  <c:v>63.986155098356939</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>64.539003450063646</c:v>
+                  <c:v>63.699223418430471</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>64.106198254993345</c:v>
+                  <c:v>60.524657455882306</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>66.309521273648855</c:v>
+                  <c:v>63.690036126164046</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>62.523738128542149</c:v>
+                  <c:v>68.393102668615157</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>69.687286369623536</c:v>
+                  <c:v>72.965816474382478</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>61.730907352530977</c:v>
+                  <c:v>69.132891507536783</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>61.341755030029134</c:v>
+                  <c:v>64.560732642842893</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>69.65492612657728</c:v>
+                  <c:v>65.06553956316084</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>69.561719211726725</c:v>
+                  <c:v>67.584435173268702</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>65.511879244613937</c:v>
+                  <c:v>63.388505838246573</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>63.400143040605201</c:v>
+                  <c:v>68.826396011148987</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>68.935900027782765</c:v>
+                  <c:v>66.901953310334136</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>58.274445673974355</c:v>
+                  <c:v>66.847864430089132</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>65.875412947247852</c:v>
+                  <c:v>63.959480931125611</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>68.3712034609309</c:v>
+                  <c:v>67.00248895781742</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>67.790685459937805</c:v>
+                  <c:v>61.846276541973559</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>67.193867540338374</c:v>
+                  <c:v>68.749918497984808</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>63.511825680366904</c:v>
+                  <c:v>67.412689056446894</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>67.699207332452957</c:v>
+                  <c:v>68.295978068811891</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>66.491354103346495</c:v>
+                  <c:v>63.508756989083238</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>67.422302083424213</c:v>
+                  <c:v>61.360217869183117</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>71.851338202611345</c:v>
+                  <c:v>70.181761015750197</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>68.52922467858356</c:v>
+                  <c:v>67.717765900309033</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>63.337405874236993</c:v>
+                  <c:v>66.949422645155238</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>65.34458773689299</c:v>
+                  <c:v>67.580467316864755</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>64.235810639210456</c:v>
+                  <c:v>65.615480189559364</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>69.085570337652257</c:v>
+                  <c:v>64.663874146530233</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>64.501702664742027</c:v>
+                  <c:v>63.554668904705267</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>64.023955392929409</c:v>
+                  <c:v>64.212661108492156</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>67.78337711608296</c:v>
+                  <c:v>63.582420345152578</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>64.917425313046166</c:v>
+                  <c:v>62.866769667379245</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>62.31059437379664</c:v>
+                  <c:v>69.763586669985443</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>67.029092748141395</c:v>
+                  <c:v>66.019920085971251</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>65.152264894695918</c:v>
+                  <c:v>68.577897562400949</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>61.199775990691577</c:v>
+                  <c:v>62.928766757172859</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>67.262455224716504</c:v>
+                  <c:v>60.650378600522203</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>64.354946312367261</c:v>
+                  <c:v>62.55492046456169</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>63.219410471693351</c:v>
+                  <c:v>64.339837049717559</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>65.831785088530282</c:v>
+                  <c:v>64.601510691071496</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>66.197320849148809</c:v>
+                  <c:v>69.18219008879332</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>62.884291193572345</c:v>
+                  <c:v>65.18081678544219</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>63.460679233636078</c:v>
+                  <c:v>62.53000958906641</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>73.396319499285866</c:v>
+                  <c:v>67.023429216239364</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>69.092637651587808</c:v>
+                  <c:v>65.419694574125401</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>64.589616250500043</c:v>
+                  <c:v>64.527943122945032</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>68.946282091601773</c:v>
+                  <c:v>63.990051817670349</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>65.383162698307871</c:v>
+                  <c:v>64.048047928929293</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>70.301066217215109</c:v>
+                  <c:v>66.004054158487477</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>70.203168423284751</c:v>
+                  <c:v>63.730839164069721</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>71.809462331261898</c:v>
+                  <c:v>64.306882565104132</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>73.447719531860685</c:v>
+                  <c:v>65.939897352211545</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>68.717819107289174</c:v>
+                  <c:v>64.462662881571831</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>72.504274540477724</c:v>
+                  <c:v>68.607508675355433</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>69.951422067288604</c:v>
+                  <c:v>64.862267423302882</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>58.303169578667131</c:v>
+                  <c:v>65.029873080459183</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>66.480416186446703</c:v>
+                  <c:v>60.474622861672934</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>68.577242095825738</c:v>
+                  <c:v>66.903253566519751</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>65.552419774222798</c:v>
+                  <c:v>61.708456177973119</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>63.471827882930448</c:v>
+                  <c:v>64.37725790007093</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>63.740992429480627</c:v>
+                  <c:v>68.591284302048706</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>61.109774491819493</c:v>
+                  <c:v>70.403276438005832</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>71.67991871011391</c:v>
+                  <c:v>62.94308564332897</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>68.559326478881999</c:v>
+                  <c:v>65.928881334843581</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>71.443183406472144</c:v>
+                  <c:v>62.630583080097253</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5674,6 +5708,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5681,7 +5716,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5999,34 +6033,34 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>59.087222836987181</c:v>
+                  <c:v>60.968868572062917</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60.7</c:v>
+                  <c:v>62.249999999999993</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>62.3</c:v>
+                  <c:v>63.54999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>63.900000000000006</c:v>
+                  <c:v>64.849999999999994</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>65.5</c:v>
+                  <c:v>66.149999999999977</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>67.099999999999994</c:v>
+                  <c:v>67.449999999999989</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>68.699999999999989</c:v>
+                  <c:v>68.749999999999972</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>70.299999999999983</c:v>
+                  <c:v>70.049999999999983</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>71.899999999999977</c:v>
+                  <c:v>71.349999999999966</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>73.499999999999972</c:v>
+                  <c:v>72.649999999999977</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6038,34 +6072,34 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>1.88</c:v>
+                  <c:v>6.15</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.38</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.63</c:v>
+                  <c:v>13.08</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12.5</c:v>
+                  <c:v>14.62</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>12.5</c:v>
+                  <c:v>13.08</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>13.13</c:v>
+                  <c:v>15.38</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>11.88</c:v>
+                  <c:v>11.54</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.1300000000000008</c:v>
+                  <c:v>7.69</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.75</c:v>
+                  <c:v>0.77</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.5</c:v>
+                  <c:v>1.54</c:v>
                 </c:pt>
                 <c:pt idx="10" formatCode="General">
                   <c:v>0</c:v>
@@ -6204,6 +6238,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6211,7 +6246,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -11276,16 +11310,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1066800</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>85723</xdr:rowOff>
+      <xdr:rowOff>104773</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>161928</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>400053</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -11300,7 +11334,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000">
-          <a:off x="4843463" y="2738435"/>
+          <a:off x="4471988" y="2757485"/>
           <a:ext cx="152402" cy="581028"/>
         </a:xfrm>
         <a:prstGeom prst="leftBrace">
@@ -11334,16 +11368,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1162050</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>481014</xdr:colOff>
+      <xdr:colOff>109539</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -11360,7 +11394,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="4724400" y="3105150"/>
+          <a:off x="4352925" y="3124200"/>
           <a:ext cx="195264" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -12004,10 +12038,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
@@ -12615,14 +12645,14 @@
       </c>
       <c r="C7" s="41">
         <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="K7" s="40" t="s">
         <v>1</v>
       </c>
       <c r="L7" s="41">
         <f ca="1">C8</f>
-        <v>18</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
@@ -12631,14 +12661,14 @@
       </c>
       <c r="C8" s="41">
         <f t="shared" ref="C8:C10" ca="1" si="0">RANDBETWEEN(1,100)</f>
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="K8" s="40" t="s">
         <v>2</v>
       </c>
       <c r="L8" s="41">
         <f ca="1">C9</f>
-        <v>21</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
@@ -12647,14 +12677,14 @@
       </c>
       <c r="C9" s="41">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="K9" s="40" t="s">
         <v>3</v>
       </c>
       <c r="L9" s="41">
         <f ca="1">C10</f>
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -12667,14 +12697,14 @@
       </c>
       <c r="C10" s="43">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="K10" s="42" t="s">
         <v>5</v>
       </c>
       <c r="L10" s="43">
         <f ca="1">C7</f>
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -12809,7 +12839,7 @@
     <row r="2" spans="2:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B3</f>
-        <v>69.475439609415915</v>
+        <v>66.242934483345223</v>
       </c>
       <c r="C2" s="45">
         <v>0.1</v>
@@ -12818,7 +12848,7 @@
     <row r="3" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B4</f>
-        <v>63.616852833726099</v>
+        <v>64.733945362871481</v>
       </c>
       <c r="C3" s="45">
         <v>0.1</v>
@@ -12837,7 +12867,7 @@
     <row r="4" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B5</f>
-        <v>65.991284820702205</v>
+        <v>66.20535912179669</v>
       </c>
       <c r="C4" s="45">
         <v>0.1</v>
@@ -12854,7 +12884,7 @@
     <row r="5" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B6</f>
-        <v>66.623824883313574</v>
+        <v>70.566312528836036</v>
       </c>
       <c r="C5" s="45">
         <v>0.1</v>
@@ -12871,7 +12901,7 @@
     <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B7</f>
-        <v>67.230278665089998</v>
+        <v>63.835344305202476</v>
       </c>
       <c r="C6" s="45">
         <v>0.1</v>
@@ -12888,7 +12918,7 @@
     <row r="7" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B8</f>
-        <v>67.918580042523629</v>
+        <v>68.12539793235554</v>
       </c>
       <c r="C7" s="45">
         <v>0.1</v>
@@ -12905,7 +12935,7 @@
     <row r="8" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B9</f>
-        <v>66.23931331263168</v>
+        <v>70.406940346506488</v>
       </c>
       <c r="C8" s="45">
         <v>0.1</v>
@@ -12922,7 +12952,7 @@
     <row r="9" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B10</f>
-        <v>66.714785283063534</v>
+        <v>68.758300257521469</v>
       </c>
       <c r="C9" s="45">
         <v>0.1</v>
@@ -12939,7 +12969,7 @@
     <row r="10" spans="2:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B11</f>
-        <v>62.717326388430067</v>
+        <v>68.052733629157672</v>
       </c>
       <c r="C10" s="45">
         <v>0.1</v>
@@ -12956,7 +12986,7 @@
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B12</f>
-        <v>72.886580462744575</v>
+        <v>60.337737144125832</v>
       </c>
       <c r="C11" s="45">
         <v>0.1</v>
@@ -12965,7 +12995,7 @@
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B13</f>
-        <v>63.360895965013576</v>
+        <v>66.232521294311383</v>
       </c>
       <c r="C12" s="45">
         <v>0.1</v>
@@ -12974,7 +13004,7 @@
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B14</f>
-        <v>70.966145710318912</v>
+        <v>66.244666483025384</v>
       </c>
       <c r="C13" s="45">
         <v>0.1</v>
@@ -12983,7 +13013,7 @@
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B15</f>
-        <v>66.463157399011621</v>
+        <v>72.926828735755066</v>
       </c>
       <c r="C14" s="45">
         <v>0.1</v>
@@ -12992,7 +13022,7 @@
     <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B16</f>
-        <v>71.375758875760511</v>
+        <v>70.680988386002909</v>
       </c>
       <c r="C15" s="45">
         <v>0.1</v>
@@ -13001,7 +13031,7 @@
     <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B17</f>
-        <v>63.376406097747228</v>
+        <v>62.879952427261607</v>
       </c>
       <c r="C16" s="45">
         <v>0.1</v>
@@ -13010,7 +13040,7 @@
     <row r="17" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B17">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B18</f>
-        <v>68.993907295192471</v>
+        <v>66.520814865113479</v>
       </c>
       <c r="C17" s="45">
         <v>0.1</v>
@@ -13019,7 +13049,7 @@
     <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B18">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B19</f>
-        <v>65.121698245632544</v>
+        <v>65.799904367928704</v>
       </c>
       <c r="C18" s="45">
         <v>0.1</v>
@@ -13031,7 +13061,7 @@
       <c r="H18" s="66"/>
       <c r="I18" s="37">
         <f ca="1">COUNTIFS(B:B,"&lt;=68",B:B,"&gt;66")</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J18" s="46"/>
       <c r="K18" s="46"/>
@@ -13039,7 +13069,7 @@
     <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B19">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B20</f>
-        <v>67.566494777888394</v>
+        <v>63.813916334643544</v>
       </c>
       <c r="C19" s="45">
         <v>0.1</v>
@@ -13051,7 +13081,7 @@
       <c r="H19" s="66"/>
       <c r="I19" s="12">
         <f ca="1">I18/COUNT(B:B)</f>
-        <v>0.21311475409836064</v>
+        <v>0.23770491803278687</v>
       </c>
       <c r="J19" s="46"/>
       <c r="K19" s="46"/>
@@ -13059,7 +13089,7 @@
     <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B20">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B21</f>
-        <v>69.580088601349573</v>
+        <v>64.136402301466291</v>
       </c>
       <c r="C20" s="45">
         <v>0.1</v>
@@ -13071,13 +13101,13 @@
       <c r="H20" s="66"/>
       <c r="I20" s="37">
         <f ca="1">I18/2</f>
-        <v>13</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B21">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B22</f>
-        <v>62.798699462229642</v>
+        <v>62.786435009059964</v>
       </c>
       <c r="C21" s="45">
         <v>0.1</v>
@@ -13089,13 +13119,13 @@
       <c r="H21" s="66"/>
       <c r="I21" s="12">
         <f ca="1">I19/2</f>
-        <v>0.10655737704918032</v>
+        <v>0.11885245901639344</v>
       </c>
     </row>
     <row r="22" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B23</f>
-        <v>61.272925749941827</v>
+        <v>69.568648923401881</v>
       </c>
       <c r="C22" s="45">
         <v>0.1</v>
@@ -13104,14 +13134,14 @@
     <row r="23" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B23">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B24</f>
-        <v>68.196609272025015</v>
+        <v>64.317414586693502</v>
       </c>
       <c r="C23" s="45">
         <v>0.1</v>
       </c>
       <c r="F23" s="53" t="str">
         <f ca="1">"The density is "&amp;I20&amp;" people (data points) per inch on the interval from 66 to 68 inches of height. While the relative density is "&amp;ROUND(I21*100,2)&amp;"% of the people per inch of height on the same interval."</f>
-        <v>The density is 13 people (data points) per inch on the interval from 66 to 68 inches of height. While the relative density is 10.66% of the people per inch of height on the same interval.</v>
+        <v>The density is 14.5 people (data points) per inch on the interval from 66 to 68 inches of height. While the relative density is 11.89% of the people per inch of height on the same interval.</v>
       </c>
       <c r="G23" s="54"/>
       <c r="H23" s="54"/>
@@ -13124,7 +13154,7 @@
     <row r="24" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B24">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B25</f>
-        <v>63.607069756577225</v>
+        <v>66.061558501820087</v>
       </c>
       <c r="C24" s="45">
         <v>0.1</v>
@@ -13141,7 +13171,7 @@
     <row r="25" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B25">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B26</f>
-        <v>66.366132304135633</v>
+        <v>65.765903101851904</v>
       </c>
       <c r="C25" s="45">
         <v>0.1</v>
@@ -13158,7 +13188,7 @@
     <row r="26" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B27</f>
-        <v>68.751086314844912</v>
+        <v>66.820491715120312</v>
       </c>
       <c r="C26" s="45">
         <v>0.1</v>
@@ -13175,7 +13205,7 @@
     <row r="27" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B27">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B28</f>
-        <v>65.873687668860754</v>
+        <v>68.263157362157685</v>
       </c>
       <c r="C27" s="45">
         <v>0.1</v>
@@ -13184,31 +13214,31 @@
     <row r="28" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B29</f>
-        <v>69.038928403175078</v>
+        <v>63.751664011456583</v>
       </c>
       <c r="C28" s="45">
         <v>0.1</v>
       </c>
     </row>
-    <row r="29" spans="2:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B30</f>
-        <v>64.79447986422656</v>
+        <v>61.139526115604589</v>
       </c>
       <c r="C29" s="45">
         <v>0.1</v>
       </c>
-      <c r="H29" s="62" t="s">
+      <c r="H29" s="82" t="s">
         <v>35</v>
       </c>
-      <c r="I29" s="63"/>
-      <c r="J29" s="63"/>
-      <c r="K29" s="64"/>
+      <c r="I29" s="83"/>
+      <c r="J29" s="83"/>
+      <c r="K29" s="84"/>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B30">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B31</f>
-        <v>68.258326414238397</v>
+        <v>61.832624825508717</v>
       </c>
       <c r="C30" s="45">
         <v>0.1</v>
@@ -13223,7 +13253,7 @@
     <row r="31" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B31">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B32</f>
-        <v>62.730611908912472</v>
+        <v>64.458155759942073</v>
       </c>
       <c r="C31" s="45">
         <v>0.1</v>
@@ -13232,7 +13262,7 @@
     <row r="32" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B32">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B33</f>
-        <v>67.732790768257743</v>
+        <v>71.43623843106856</v>
       </c>
       <c r="C32" s="45">
         <v>0.1</v>
@@ -13241,7 +13271,7 @@
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B34</f>
-        <v>67.732008088296539</v>
+        <v>70.380261068021241</v>
       </c>
       <c r="C33" s="45">
         <v>0.1</v>
@@ -13250,7 +13280,7 @@
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B35</f>
-        <v>66.933572867587372</v>
+        <v>67.958562513892531</v>
       </c>
       <c r="C34" s="45">
         <v>0.1</v>
@@ -13259,7 +13289,7 @@
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B36</f>
-        <v>68.250670132527418</v>
+        <v>67.050559490969547</v>
       </c>
       <c r="C35" s="45">
         <v>0.1</v>
@@ -13268,7 +13298,7 @@
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B37</f>
-        <v>59.661817353543697</v>
+        <v>67.724337352905977</v>
       </c>
       <c r="C36" s="45">
         <v>0.1</v>
@@ -13277,7 +13307,7 @@
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B38</f>
-        <v>60.09508594830038</v>
+        <v>62.770845880537131</v>
       </c>
       <c r="C37" s="45">
         <v>0.1</v>
@@ -13286,7 +13316,7 @@
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B39</f>
-        <v>70.787846692610145</v>
+        <v>62.293042269721461</v>
       </c>
       <c r="C38" s="45">
         <v>0.1</v>
@@ -13295,7 +13325,7 @@
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B40</f>
-        <v>69.66281205015099</v>
+        <v>65.536563806302993</v>
       </c>
       <c r="C39" s="45">
         <v>0.1</v>
@@ -13304,7 +13334,7 @@
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B41</f>
-        <v>69.01873232943548</v>
+        <v>67.207745864465835</v>
       </c>
       <c r="C40" s="45">
         <v>0.1</v>
@@ -13313,7 +13343,7 @@
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B42</f>
-        <v>72.904379406546724</v>
+        <v>62.547370272693669</v>
       </c>
       <c r="C41" s="45">
         <v>0.1</v>
@@ -13322,7 +13352,7 @@
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B43</f>
-        <v>66.741820053561838</v>
+        <v>69.392140184375819</v>
       </c>
       <c r="C42" s="45">
         <v>0.1</v>
@@ -13331,7 +13361,7 @@
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B44</f>
-        <v>65.407956382634339</v>
+        <v>67.729854637108858</v>
       </c>
       <c r="C43" s="45">
         <v>0.1</v>
@@ -13340,7 +13370,7 @@
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B45</f>
-        <v>67.248773020074722</v>
+        <v>66.083867300281312</v>
       </c>
       <c r="C44" s="45">
         <v>0.1</v>
@@ -13349,7 +13379,7 @@
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B46</f>
-        <v>63.616341912223312</v>
+        <v>67.317733735635542</v>
       </c>
       <c r="C45" s="45">
         <v>0.1</v>
@@ -13358,7 +13388,7 @@
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B47</f>
-        <v>66.016419424342288</v>
+        <v>66.770176536641756</v>
       </c>
       <c r="C46" s="45">
         <v>0.1</v>
@@ -13367,7 +13397,7 @@
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B48</f>
-        <v>69.57620562002127</v>
+        <v>65.802601715232484</v>
       </c>
       <c r="C47" s="45">
         <v>0.1</v>
@@ -13376,7 +13406,7 @@
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B49</f>
-        <v>65.660848371674192</v>
+        <v>60.686868681992188</v>
       </c>
       <c r="C48" s="45">
         <v>0.1</v>
@@ -13385,7 +13415,7 @@
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B50</f>
-        <v>62.368526769562038</v>
+        <v>70.631436966120845</v>
       </c>
       <c r="C49" s="45">
         <v>0.1</v>
@@ -13394,7 +13424,7 @@
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B51</f>
-        <v>63.234695801963049</v>
+        <v>67.822231309414491</v>
       </c>
       <c r="C50" s="45">
         <v>0.1</v>
@@ -13403,7 +13433,7 @@
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B52</f>
-        <v>69.877266762241959</v>
+        <v>65.451083517140262</v>
       </c>
       <c r="C51" s="45">
         <v>0.1</v>
@@ -13412,7 +13442,7 @@
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B53</f>
-        <v>68.614950776555119</v>
+        <v>69.889156638810135</v>
       </c>
       <c r="C52" s="45">
         <v>0.1</v>
@@ -13421,7 +13451,7 @@
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B54</f>
-        <v>60.223604529459777</v>
+        <v>62.575792941732757</v>
       </c>
       <c r="C53" s="45">
         <v>0.1</v>
@@ -13430,7 +13460,7 @@
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B55</f>
-        <v>70.803936966712754</v>
+        <v>68.790168500099284</v>
       </c>
       <c r="C54" s="45">
         <v>0.1</v>
@@ -13439,7 +13469,7 @@
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B56</f>
-        <v>65.406153874396821</v>
+        <v>65.195396415878776</v>
       </c>
       <c r="C55" s="45">
         <v>0.1</v>
@@ -13448,7 +13478,7 @@
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B57</f>
-        <v>62.478361733531543</v>
+        <v>67.083526236133267</v>
       </c>
       <c r="C56" s="45">
         <v>0.1</v>
@@ -13457,7 +13487,7 @@
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B58</f>
-        <v>65.733687038141014</v>
+        <v>69.226471004443937</v>
       </c>
       <c r="C57" s="45">
         <v>0.1</v>
@@ -13466,7 +13496,7 @@
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B59</f>
-        <v>61.344876881641696</v>
+        <v>61.030827750936695</v>
       </c>
       <c r="C58" s="45">
         <v>0.1</v>
@@ -13475,7 +13505,7 @@
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B60</f>
-        <v>66.240712540221054</v>
+        <v>63.986155098356939</v>
       </c>
       <c r="C59" s="45">
         <v>0.1</v>
@@ -13484,7 +13514,7 @@
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B61</f>
-        <v>64.539003450063646</v>
+        <v>63.699223418430471</v>
       </c>
       <c r="C60" s="45">
         <v>0.1</v>
@@ -13493,7 +13523,7 @@
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B62</f>
-        <v>64.106198254993345</v>
+        <v>60.524657455882306</v>
       </c>
       <c r="C61" s="45">
         <v>0.1</v>
@@ -13502,7 +13532,7 @@
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B63</f>
-        <v>66.309521273648855</v>
+        <v>63.690036126164046</v>
       </c>
       <c r="C62" s="45">
         <v>0.1</v>
@@ -13511,7 +13541,7 @@
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B64</f>
-        <v>62.523738128542149</v>
+        <v>68.393102668615157</v>
       </c>
       <c r="C63" s="45">
         <v>0.1</v>
@@ -13520,7 +13550,7 @@
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B65</f>
-        <v>69.687286369623536</v>
+        <v>72.965816474382478</v>
       </c>
       <c r="C64" s="45">
         <v>0.1</v>
@@ -13529,7 +13559,7 @@
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B66</f>
-        <v>61.730907352530977</v>
+        <v>69.132891507536783</v>
       </c>
       <c r="C65" s="45">
         <v>0.1</v>
@@ -13538,7 +13568,7 @@
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B67</f>
-        <v>61.341755030029134</v>
+        <v>64.560732642842893</v>
       </c>
       <c r="C66" s="45">
         <v>0.1</v>
@@ -13547,7 +13577,7 @@
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B68</f>
-        <v>69.65492612657728</v>
+        <v>65.06553956316084</v>
       </c>
       <c r="C67" s="45">
         <v>0.1</v>
@@ -13556,7 +13586,7 @@
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B69</f>
-        <v>69.561719211726725</v>
+        <v>67.584435173268702</v>
       </c>
       <c r="C68" s="45">
         <v>0.1</v>
@@ -13565,7 +13595,7 @@
     <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B70</f>
-        <v>65.511879244613937</v>
+        <v>63.388505838246573</v>
       </c>
       <c r="C69" s="45">
         <v>0.1</v>
@@ -13574,7 +13604,7 @@
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B71</f>
-        <v>63.400143040605201</v>
+        <v>68.826396011148987</v>
       </c>
       <c r="C70" s="45">
         <v>0.1</v>
@@ -13583,7 +13613,7 @@
     <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B72</f>
-        <v>68.935900027782765</v>
+        <v>66.901953310334136</v>
       </c>
       <c r="C71" s="45">
         <v>0.1</v>
@@ -13592,7 +13622,7 @@
     <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B73</f>
-        <v>58.274445673974355</v>
+        <v>66.847864430089132</v>
       </c>
       <c r="C72" s="45">
         <v>0.1</v>
@@ -13601,7 +13631,7 @@
     <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B74</f>
-        <v>65.875412947247852</v>
+        <v>63.959480931125611</v>
       </c>
       <c r="C73" s="45">
         <v>0.1</v>
@@ -13610,7 +13640,7 @@
     <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B75</f>
-        <v>68.3712034609309</v>
+        <v>67.00248895781742</v>
       </c>
       <c r="C74" s="45">
         <v>0.1</v>
@@ -13619,7 +13649,7 @@
     <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B76</f>
-        <v>67.790685459937805</v>
+        <v>61.846276541973559</v>
       </c>
       <c r="C75" s="45">
         <v>0.1</v>
@@ -13628,7 +13658,7 @@
     <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B77</f>
-        <v>67.193867540338374</v>
+        <v>68.749918497984808</v>
       </c>
       <c r="C76" s="45">
         <v>0.1</v>
@@ -13637,7 +13667,7 @@
     <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B78</f>
-        <v>63.511825680366904</v>
+        <v>67.412689056446894</v>
       </c>
       <c r="C77" s="45">
         <v>0.1</v>
@@ -13646,7 +13676,7 @@
     <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B79</f>
-        <v>67.699207332452957</v>
+        <v>68.295978068811891</v>
       </c>
       <c r="C78" s="45">
         <v>0.1</v>
@@ -13655,7 +13685,7 @@
     <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B80</f>
-        <v>66.491354103346495</v>
+        <v>63.508756989083238</v>
       </c>
       <c r="C79" s="45">
         <v>0.1</v>
@@ -13664,7 +13694,7 @@
     <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B81</f>
-        <v>67.422302083424213</v>
+        <v>61.360217869183117</v>
       </c>
       <c r="C80" s="45">
         <v>0.1</v>
@@ -13673,7 +13703,7 @@
     <row r="81" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B81">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B82</f>
-        <v>71.851338202611345</v>
+        <v>70.181761015750197</v>
       </c>
       <c r="C81" s="45">
         <v>0.1</v>
@@ -13682,7 +13712,7 @@
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B82">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B83</f>
-        <v>68.52922467858356</v>
+        <v>67.717765900309033</v>
       </c>
       <c r="C82" s="45">
         <v>0.1</v>
@@ -13691,7 +13721,7 @@
     <row r="83" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B83">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B84</f>
-        <v>63.337405874236993</v>
+        <v>66.949422645155238</v>
       </c>
       <c r="C83" s="45">
         <v>0.1</v>
@@ -13700,7 +13730,7 @@
     <row r="84" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B84">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B85</f>
-        <v>65.34458773689299</v>
+        <v>67.580467316864755</v>
       </c>
       <c r="C84" s="45">
         <v>0.1</v>
@@ -13709,7 +13739,7 @@
     <row r="85" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B85">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B86</f>
-        <v>64.235810639210456</v>
+        <v>65.615480189559364</v>
       </c>
       <c r="C85" s="45">
         <v>0.1</v>
@@ -13718,7 +13748,7 @@
     <row r="86" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B86">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B87</f>
-        <v>69.085570337652257</v>
+        <v>64.663874146530233</v>
       </c>
       <c r="C86" s="45">
         <v>0.1</v>
@@ -13727,7 +13757,7 @@
     <row r="87" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B87">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B88</f>
-        <v>64.501702664742027</v>
+        <v>63.554668904705267</v>
       </c>
       <c r="C87" s="45">
         <v>0.1</v>
@@ -13736,7 +13766,7 @@
     <row r="88" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B88">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B89</f>
-        <v>64.023955392929409</v>
+        <v>64.212661108492156</v>
       </c>
       <c r="C88" s="45">
         <v>0.1</v>
@@ -13745,7 +13775,7 @@
     <row r="89" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B89">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B90</f>
-        <v>67.78337711608296</v>
+        <v>63.582420345152578</v>
       </c>
       <c r="C89" s="45">
         <v>0.1</v>
@@ -13754,7 +13784,7 @@
     <row r="90" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B90">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B91</f>
-        <v>64.917425313046166</v>
+        <v>62.866769667379245</v>
       </c>
       <c r="C90" s="45">
         <v>0.1</v>
@@ -13763,7 +13793,7 @@
     <row r="91" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B91">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B92</f>
-        <v>62.31059437379664</v>
+        <v>69.763586669985443</v>
       </c>
       <c r="C91" s="45">
         <v>0.1</v>
@@ -13772,7 +13802,7 @@
     <row r="92" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B92">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B93</f>
-        <v>67.029092748141395</v>
+        <v>66.019920085971251</v>
       </c>
       <c r="C92" s="45">
         <v>0.1</v>
@@ -13781,7 +13811,7 @@
     <row r="93" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B93">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B94</f>
-        <v>65.152264894695918</v>
+        <v>68.577897562400949</v>
       </c>
       <c r="C93" s="45">
         <v>0.1</v>
@@ -13790,7 +13820,7 @@
     <row r="94" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B94">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B95</f>
-        <v>61.199775990691577</v>
+        <v>62.928766757172859</v>
       </c>
       <c r="C94" s="45">
         <v>0.1</v>
@@ -13799,7 +13829,7 @@
     <row r="95" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B95">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B96</f>
-        <v>67.262455224716504</v>
+        <v>60.650378600522203</v>
       </c>
       <c r="C95" s="45">
         <v>0.1</v>
@@ -13808,7 +13838,7 @@
     <row r="96" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B96">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B97</f>
-        <v>64.354946312367261</v>
+        <v>62.55492046456169</v>
       </c>
       <c r="C96" s="45">
         <v>0.1</v>
@@ -13817,7 +13847,7 @@
     <row r="97" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B97">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B98</f>
-        <v>63.219410471693351</v>
+        <v>64.339837049717559</v>
       </c>
       <c r="C97" s="45">
         <v>0.1</v>
@@ -13826,7 +13856,7 @@
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B98">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B99</f>
-        <v>65.831785088530282</v>
+        <v>64.601510691071496</v>
       </c>
       <c r="C98" s="45">
         <v>0.1</v>
@@ -13835,7 +13865,7 @@
     <row r="99" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B99">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B100</f>
-        <v>66.197320849148809</v>
+        <v>69.18219008879332</v>
       </c>
       <c r="C99" s="45">
         <v>0.1</v>
@@ -13844,7 +13874,7 @@
     <row r="100" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B100">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B101</f>
-        <v>62.884291193572345</v>
+        <v>65.18081678544219</v>
       </c>
       <c r="C100" s="45">
         <v>0.1</v>
@@ -13853,7 +13883,7 @@
     <row r="101" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B101">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B102</f>
-        <v>63.460679233636078</v>
+        <v>62.53000958906641</v>
       </c>
       <c r="C101" s="45">
         <v>0.1</v>
@@ -13862,7 +13892,7 @@
     <row r="102" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B102">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B103</f>
-        <v>73.396319499285866</v>
+        <v>67.023429216239364</v>
       </c>
       <c r="C102" s="45">
         <v>0.1</v>
@@ -13871,7 +13901,7 @@
     <row r="103" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B103">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B104</f>
-        <v>69.092637651587808</v>
+        <v>65.419694574125401</v>
       </c>
       <c r="C103" s="45">
         <v>0.1</v>
@@ -13880,7 +13910,7 @@
     <row r="104" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B104">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B105</f>
-        <v>64.589616250500043</v>
+        <v>64.527943122945032</v>
       </c>
       <c r="C104" s="45">
         <v>0.1</v>
@@ -13889,7 +13919,7 @@
     <row r="105" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B105">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B106</f>
-        <v>68.946282091601773</v>
+        <v>63.990051817670349</v>
       </c>
       <c r="C105" s="45">
         <v>0.1</v>
@@ -13898,7 +13928,7 @@
     <row r="106" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B106">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B107</f>
-        <v>65.383162698307871</v>
+        <v>64.048047928929293</v>
       </c>
       <c r="C106" s="45">
         <v>0.1</v>
@@ -13907,7 +13937,7 @@
     <row r="107" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B107">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B108</f>
-        <v>70.301066217215109</v>
+        <v>66.004054158487477</v>
       </c>
       <c r="C107" s="45">
         <v>0.1</v>
@@ -13916,7 +13946,7 @@
     <row r="108" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B108">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B109</f>
-        <v>70.203168423284751</v>
+        <v>63.730839164069721</v>
       </c>
       <c r="C108" s="45">
         <v>0.1</v>
@@ -13925,7 +13955,7 @@
     <row r="109" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B109">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B110</f>
-        <v>71.809462331261898</v>
+        <v>64.306882565104132</v>
       </c>
       <c r="C109" s="45">
         <v>0.1</v>
@@ -13934,7 +13964,7 @@
     <row r="110" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B110">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B111</f>
-        <v>73.447719531860685</v>
+        <v>65.939897352211545</v>
       </c>
       <c r="C110" s="45">
         <v>0.1</v>
@@ -13943,7 +13973,7 @@
     <row r="111" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B111">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B112</f>
-        <v>68.717819107289174</v>
+        <v>64.462662881571831</v>
       </c>
       <c r="C111" s="45">
         <v>0.1</v>
@@ -13952,7 +13982,7 @@
     <row r="112" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B112">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B113</f>
-        <v>72.504274540477724</v>
+        <v>68.607508675355433</v>
       </c>
       <c r="C112" s="45">
         <v>0.1</v>
@@ -13961,7 +13991,7 @@
     <row r="113" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B113">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B114</f>
-        <v>69.951422067288604</v>
+        <v>64.862267423302882</v>
       </c>
       <c r="C113" s="45">
         <v>0.1</v>
@@ -13970,7 +14000,7 @@
     <row r="114" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B114">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B115</f>
-        <v>58.303169578667131</v>
+        <v>65.029873080459183</v>
       </c>
       <c r="C114" s="45">
         <v>0.1</v>
@@ -13979,7 +14009,7 @@
     <row r="115" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B115">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B116</f>
-        <v>66.480416186446703</v>
+        <v>60.474622861672934</v>
       </c>
       <c r="C115" s="45">
         <v>0.1</v>
@@ -13988,7 +14018,7 @@
     <row r="116" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B116">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B117</f>
-        <v>68.577242095825738</v>
+        <v>66.903253566519751</v>
       </c>
       <c r="C116" s="45">
         <v>0.1</v>
@@ -13997,7 +14027,7 @@
     <row r="117" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B117">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B118</f>
-        <v>65.552419774222798</v>
+        <v>61.708456177973119</v>
       </c>
       <c r="C117" s="45">
         <v>0.1</v>
@@ -14006,7 +14036,7 @@
     <row r="118" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B118">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B119</f>
-        <v>63.471827882930448</v>
+        <v>64.37725790007093</v>
       </c>
       <c r="C118" s="45">
         <v>0.1</v>
@@ -14015,7 +14045,7 @@
     <row r="119" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B119">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B120</f>
-        <v>63.740992429480627</v>
+        <v>68.591284302048706</v>
       </c>
       <c r="C119" s="45">
         <v>0.1</v>
@@ -14024,7 +14054,7 @@
     <row r="120" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B120">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B121</f>
-        <v>61.109774491819493</v>
+        <v>70.403276438005832</v>
       </c>
       <c r="C120" s="45">
         <v>0.1</v>
@@ -14033,7 +14063,7 @@
     <row r="121" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B121">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B122</f>
-        <v>71.67991871011391</v>
+        <v>62.94308564332897</v>
       </c>
       <c r="C121" s="45">
         <v>0.1</v>
@@ -14042,7 +14072,7 @@
     <row r="122" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B122">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B123</f>
-        <v>68.559326478881999</v>
+        <v>65.928881334843581</v>
       </c>
       <c r="C122" s="45">
         <v>0.1</v>
@@ -14051,7 +14081,7 @@
     <row r="123" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B123">
         <f ca="1">'Histogram (Unequal Bin Widths)'!B124</f>
-        <v>71.443183406472144</v>
+        <v>62.630583080097253</v>
       </c>
       <c r="C123" s="45">
         <v>0.1</v>
@@ -14059,14 +14089,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="H29:K29"/>
+    <mergeCell ref="H30:K30"/>
     <mergeCell ref="F3:M10"/>
     <mergeCell ref="F18:H18"/>
     <mergeCell ref="F19:H19"/>
     <mergeCell ref="F23:M26"/>
     <mergeCell ref="F20:H20"/>
     <mergeCell ref="F21:H21"/>
-    <mergeCell ref="H29:K29"/>
-    <mergeCell ref="H30:K30"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H29:K29" r:id="rId1" display="Video For this." xr:uid="{D7D24FF2-9F91-4E6A-B685-E256AC63C8D0}"/>
@@ -14109,7 +14139,7 @@
     <row r="3" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B3" s="14">
         <f ca="1">_xlfn.NORM.INV(RAND(),66,3)</f>
-        <v>69.475439609415915</v>
+        <v>66.242934483345223</v>
       </c>
       <c r="E3" s="67"/>
       <c r="F3" s="68"/>
@@ -14119,92 +14149,92 @@
     <row r="4" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B4" s="14">
         <f t="shared" ref="B4:B67" ca="1" si="0">_xlfn.NORM.INV(RAND(),66,3)</f>
-        <v>63.616852833726099</v>
+        <v>64.733945362871481</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="38">
         <f ca="1">MAX(B:B)</f>
-        <v>73.447719531860685</v>
+        <v>72.965816474382478</v>
       </c>
       <c r="E4" s="13">
         <f ca="1">ROUND(D5,1)+D6</f>
-        <v>59.9</v>
+        <v>61.599999999999994</v>
       </c>
       <c r="F4" s="4" cm="1">
         <f t="array" aca="1" ref="F4:F13" ca="1">FREQUENCY(B:B,E4:E12)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G4" s="15" cm="1">
         <f t="array" aca="1" ref="G4:G13" ca="1">_xlfn.ANCHORARRAY(F4)/COUNT(B:B)</f>
-        <v>2.4590163934426229E-2</v>
+        <v>6.5573770491803282E-2</v>
       </c>
       <c r="H4" s="13">
         <f ca="1">(D5+E4)/2</f>
-        <v>59.087222836987181</v>
+        <v>60.968868572062917</v>
       </c>
     </row>
     <row r="5" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>65.991284820702205</v>
+        <v>66.20535912179669</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="38">
         <f ca="1">MIN(B:B)</f>
-        <v>58.274445673974355</v>
+        <v>60.337737144125832</v>
       </c>
       <c r="E5" s="13">
         <f ca="1">E4+D$6</f>
-        <v>61.5</v>
+        <v>62.899999999999991</v>
       </c>
       <c r="F5" s="4">
         <f ca="1"/>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G5" s="15">
         <f ca="1"/>
-        <v>5.737704918032787E-2</v>
+        <v>0.10655737704918032</v>
       </c>
       <c r="H5" s="13">
         <f ca="1">(E4+E5)/2</f>
-        <v>60.7</v>
+        <v>62.249999999999993</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B6" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>66.623824883313574</v>
+        <v>70.566312528836036</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="11">
         <f ca="1">ROUNDUP((D4-D5)/10,1)</f>
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="E6" s="13">
         <f t="shared" ref="E6:E13" ca="1" si="1">E5+D$6</f>
-        <v>63.1</v>
+        <v>64.199999999999989</v>
       </c>
       <c r="F6" s="4">
         <f ca="1"/>
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G6" s="15">
         <f ca="1"/>
-        <v>7.3770491803278687E-2</v>
+        <v>0.13934426229508196</v>
       </c>
       <c r="H6" s="13">
         <f t="shared" ref="H6:H13" ca="1" si="2">(E5+E6)/2</f>
-        <v>62.3</v>
+        <v>63.54999999999999</v>
       </c>
       <c r="P6" s="53" t="str">
         <f ca="1">"In a frequency histogram the area of a region should correspond to the number of points on the x-axis lying in that region. This chart, which is often called a histogram, is really still not quite a histogram. Take one of the bars. The area of the bar is "&amp;D6*F9&amp;", but the number of data points represented by the bar is "&amp;F9&amp;"."</f>
-        <v>In a frequency histogram the area of a region should correspond to the number of points on the x-axis lying in that region. This chart, which is often called a histogram, is really still not quite a histogram. Take one of the bars. The area of the bar is 33.6, but the number of data points represented by the bar is 21.</v>
+        <v>In a frequency histogram the area of a region should correspond to the number of points on the x-axis lying in that region. This chart, which is often called a histogram, is really still not quite a histogram. Take one of the bars. The area of the bar is 26, but the number of data points represented by the bar is 20.</v>
       </c>
       <c r="Q6" s="54"/>
       <c r="R6" s="54"/>
@@ -14215,23 +14245,23 @@
     <row r="7" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B7" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>67.230278665089998</v>
+        <v>63.835344305202476</v>
       </c>
       <c r="E7" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>64.7</v>
+        <v>65.499999999999986</v>
       </c>
       <c r="F7" s="4">
         <f ca="1"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" s="15">
         <f ca="1"/>
-        <v>0.16393442622950818</v>
+        <v>0.15573770491803279</v>
       </c>
       <c r="H7" s="13">
         <f t="shared" ca="1" si="2"/>
-        <v>63.900000000000006</v>
+        <v>64.849999999999994</v>
       </c>
       <c r="P7" s="56"/>
       <c r="Q7" s="57"/>
@@ -14243,23 +14273,23 @@
     <row r="8" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B8" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>67.918580042523629</v>
+        <v>68.12539793235554</v>
       </c>
       <c r="E8" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>66.3</v>
+        <v>66.799999999999983</v>
       </c>
       <c r="F8" s="4">
         <f ca="1"/>
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G8" s="15">
         <f ca="1"/>
-        <v>0.16393442622950818</v>
+        <v>0.13934426229508196</v>
       </c>
       <c r="H8" s="13">
         <f t="shared" ca="1" si="2"/>
-        <v>65.5</v>
+        <v>66.149999999999977</v>
       </c>
       <c r="P8" s="56"/>
       <c r="Q8" s="57"/>
@@ -14271,23 +14301,23 @@
     <row r="9" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>66.23931331263168</v>
+        <v>70.406940346506488</v>
       </c>
       <c r="E9" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>67.899999999999991</v>
+        <v>68.09999999999998</v>
       </c>
       <c r="F9" s="47">
         <f ca="1"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G9" s="48">
         <f ca="1"/>
-        <v>0.1721311475409836</v>
+        <v>0.16393442622950818</v>
       </c>
       <c r="H9" s="13">
         <f t="shared" ca="1" si="2"/>
-        <v>67.099999999999994</v>
+        <v>67.449999999999989</v>
       </c>
       <c r="P9" s="56"/>
       <c r="Q9" s="57"/>
@@ -14299,23 +14329,23 @@
     <row r="10" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>66.714785283063534</v>
+        <v>68.758300257521469</v>
       </c>
       <c r="E10" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>69.499999999999986</v>
+        <v>69.399999999999977</v>
       </c>
       <c r="F10" s="4">
         <f ca="1"/>
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G10" s="15">
         <f ca="1"/>
-        <v>0.15573770491803279</v>
+        <v>0.12295081967213115</v>
       </c>
       <c r="H10" s="13">
         <f t="shared" ca="1" si="2"/>
-        <v>68.699999999999989</v>
+        <v>68.749999999999972</v>
       </c>
       <c r="P10" s="56"/>
       <c r="Q10" s="57"/>
@@ -14327,23 +14357,23 @@
     <row r="11" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>62.717326388430067</v>
+        <v>68.052733629157672</v>
       </c>
       <c r="E11" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>71.09999999999998</v>
+        <v>70.699999999999974</v>
       </c>
       <c r="F11" s="4">
         <f ca="1"/>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G11" s="15">
         <f ca="1"/>
-        <v>0.10655737704918032</v>
+        <v>8.1967213114754092E-2</v>
       </c>
       <c r="H11" s="13">
         <f t="shared" ca="1" si="2"/>
-        <v>70.299999999999983</v>
+        <v>70.049999999999983</v>
       </c>
       <c r="P11" s="56"/>
       <c r="Q11" s="57"/>
@@ -14355,23 +14385,23 @@
     <row r="12" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>72.886580462744575</v>
+        <v>60.337737144125832</v>
       </c>
       <c r="E12" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>72.699999999999974</v>
+        <v>71.999999999999972</v>
       </c>
       <c r="F12" s="4">
         <f ca="1"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G12" s="15">
         <f ca="1"/>
-        <v>4.9180327868852458E-2</v>
+        <v>8.1967213114754103E-3</v>
       </c>
       <c r="H12" s="13">
         <f t="shared" ca="1" si="2"/>
-        <v>71.899999999999977</v>
+        <v>71.349999999999966</v>
       </c>
       <c r="P12" s="56"/>
       <c r="Q12" s="57"/>
@@ -14383,23 +14413,23 @@
     <row r="13" spans="2:21" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>63.360895965013576</v>
+        <v>66.232521294311383</v>
       </c>
       <c r="E13" s="13">
         <f t="shared" ca="1" si="1"/>
-        <v>74.299999999999969</v>
+        <v>73.299999999999969</v>
       </c>
       <c r="F13" s="4">
         <f ca="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G13" s="15">
         <f ca="1"/>
-        <v>3.2786885245901641E-2</v>
+        <v>1.6393442622950821E-2</v>
       </c>
       <c r="H13" s="13">
         <f t="shared" ca="1" si="2"/>
-        <v>73.499999999999972</v>
+        <v>72.649999999999977</v>
       </c>
       <c r="P13" s="59"/>
       <c r="Q13" s="60"/>
@@ -14411,7 +14441,7 @@
     <row r="14" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>70.966145710318912</v>
+        <v>66.244666483025384</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>13</v>
@@ -14428,19 +14458,19 @@
     <row r="15" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>66.463157399011621</v>
+        <v>72.926828735755066</v>
       </c>
     </row>
     <row r="16" spans="2:21" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>71.375758875760511</v>
+        <v>70.680988386002909</v>
       </c>
     </row>
     <row r="17" spans="2:21" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>63.376406097747228</v>
+        <v>62.879952427261607</v>
       </c>
       <c r="D17" s="53" t="s">
         <v>21</v>
@@ -14451,14 +14481,14 @@
     <row r="18" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>68.993907295192471</v>
+        <v>66.520814865113479</v>
       </c>
       <c r="D18" s="56"/>
       <c r="E18" s="57"/>
       <c r="F18" s="58"/>
       <c r="P18" s="53" t="str">
         <f ca="1">"In a relative frequency histogram the area of a region should correspond to the percentage of "&amp;"points on the x-axis lying in that region. This chart, which is often called a histogram, is really still not quite a histogram. Take one of the bars again. The area of the bar is "&amp;ROUND(D6*G9*100,2)&amp;"%, but the percentage of data points represented by the bar is "&amp;ROUND(G9*100,2)&amp;"%."</f>
-        <v>In a relative frequency histogram the area of a region should correspond to the percentage of points on the x-axis lying in that region. This chart, which is often called a histogram, is really still not quite a histogram. Take one of the bars again. The area of the bar is 27.54%, but the percentage of data points represented by the bar is 17.21%.</v>
+        <v>In a relative frequency histogram the area of a region should correspond to the percentage of points on the x-axis lying in that region. This chart, which is often called a histogram, is really still not quite a histogram. Take one of the bars again. The area of the bar is 21.31%, but the percentage of data points represented by the bar is 16.39%.</v>
       </c>
       <c r="Q18" s="54"/>
       <c r="R18" s="54"/>
@@ -14469,7 +14499,7 @@
     <row r="19" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>65.121698245632544</v>
+        <v>65.799904367928704</v>
       </c>
       <c r="D19" s="56"/>
       <c r="E19" s="57"/>
@@ -14484,7 +14514,7 @@
     <row r="20" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>67.566494777888394</v>
+        <v>63.813916334643544</v>
       </c>
       <c r="D20" s="56"/>
       <c r="E20" s="57"/>
@@ -14499,7 +14529,7 @@
     <row r="21" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>69.580088601349573</v>
+        <v>64.136402301466291</v>
       </c>
       <c r="D21" s="56"/>
       <c r="E21" s="57"/>
@@ -14514,7 +14544,7 @@
     <row r="22" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B22" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>62.798699462229642</v>
+        <v>62.786435009059964</v>
       </c>
       <c r="D22" s="56"/>
       <c r="E22" s="57"/>
@@ -14529,7 +14559,7 @@
     <row r="23" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>61.272925749941827</v>
+        <v>69.568648923401881</v>
       </c>
       <c r="D23" s="59"/>
       <c r="E23" s="60"/>
@@ -14544,7 +14574,7 @@
     <row r="24" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B24" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>68.196609272025015</v>
+        <v>64.317414586693502</v>
       </c>
       <c r="P24" s="56"/>
       <c r="Q24" s="57"/>
@@ -14556,7 +14586,7 @@
     <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B25" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>63.607069756577225</v>
+        <v>66.061558501820087</v>
       </c>
       <c r="P25" s="56"/>
       <c r="Q25" s="57"/>
@@ -14568,7 +14598,7 @@
     <row r="26" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>66.366132304135633</v>
+        <v>65.765903101851904</v>
       </c>
       <c r="P26" s="59"/>
       <c r="Q26" s="60"/>
@@ -14580,61 +14610,61 @@
     <row r="27" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B27" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>68.751086314844912</v>
+        <v>66.820491715120312</v>
       </c>
     </row>
     <row r="28" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B28" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>65.873687668860754</v>
+        <v>68.263157362157685</v>
       </c>
     </row>
     <row r="29" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B29" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>69.038928403175078</v>
+        <v>63.751664011456583</v>
       </c>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B30" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>64.79447986422656</v>
+        <v>61.139526115604589</v>
       </c>
     </row>
     <row r="31" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B31" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>68.258326414238397</v>
+        <v>61.832624825508717</v>
       </c>
     </row>
     <row r="32" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>62.730611908912472</v>
+        <v>64.458155759942073</v>
       </c>
     </row>
     <row r="33" spans="2:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>67.732790768257743</v>
+        <v>71.43623843106856</v>
       </c>
     </row>
     <row r="34" spans="2:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>67.732008088296539</v>
-      </c>
-      <c r="I34" s="62" t="s">
+        <v>70.380261068021241</v>
+      </c>
+      <c r="I34" s="79" t="s">
         <v>35</v>
       </c>
-      <c r="J34" s="63"/>
-      <c r="K34" s="63"/>
-      <c r="L34" s="64"/>
+      <c r="J34" s="80"/>
+      <c r="K34" s="80"/>
+      <c r="L34" s="81"/>
     </row>
     <row r="35" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>66.933572867587372</v>
+        <v>67.958562513892531</v>
       </c>
       <c r="I35" s="65" t="s">
         <v>36</v>
@@ -14646,535 +14676,535 @@
     <row r="36" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>68.250670132527418</v>
+        <v>67.050559490969547</v>
       </c>
     </row>
     <row r="37" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>59.661817353543697</v>
+        <v>67.724337352905977</v>
       </c>
     </row>
     <row r="38" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>60.09508594830038</v>
+        <v>62.770845880537131</v>
       </c>
     </row>
     <row r="39" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>70.787846692610145</v>
+        <v>62.293042269721461</v>
       </c>
     </row>
     <row r="40" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>69.66281205015099</v>
+        <v>65.536563806302993</v>
       </c>
     </row>
     <row r="41" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>69.01873232943548</v>
+        <v>67.207745864465835</v>
       </c>
     </row>
     <row r="42" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>72.904379406546724</v>
+        <v>62.547370272693669</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B43" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>66.741820053561838</v>
+        <v>69.392140184375819</v>
       </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B44" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>65.407956382634339</v>
+        <v>67.729854637108858</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B45" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>67.248773020074722</v>
+        <v>66.083867300281312</v>
       </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B46" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>63.616341912223312</v>
+        <v>67.317733735635542</v>
       </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B47" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>66.016419424342288</v>
+        <v>66.770176536641756</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B48" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>69.57620562002127</v>
+        <v>65.802601715232484</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>65.660848371674192</v>
+        <v>60.686868681992188</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B50" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>62.368526769562038</v>
+        <v>70.631436966120845</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B51" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>63.234695801963049</v>
+        <v>67.822231309414491</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B52" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>69.877266762241959</v>
+        <v>65.451083517140262</v>
       </c>
     </row>
     <row r="53" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B53" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>68.614950776555119</v>
+        <v>69.889156638810135</v>
       </c>
     </row>
     <row r="54" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B54" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>60.223604529459777</v>
+        <v>62.575792941732757</v>
       </c>
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B55" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>70.803936966712754</v>
+        <v>68.790168500099284</v>
       </c>
     </row>
     <row r="56" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B56" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>65.406153874396821</v>
+        <v>65.195396415878776</v>
       </c>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B57" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>62.478361733531543</v>
+        <v>67.083526236133267</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B58" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>65.733687038141014</v>
+        <v>69.226471004443937</v>
       </c>
     </row>
     <row r="59" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B59" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>61.344876881641696</v>
+        <v>61.030827750936695</v>
       </c>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B60" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>66.240712540221054</v>
+        <v>63.986155098356939</v>
       </c>
     </row>
     <row r="61" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B61" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>64.539003450063646</v>
+        <v>63.699223418430471</v>
       </c>
     </row>
     <row r="62" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B62" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>64.106198254993345</v>
+        <v>60.524657455882306</v>
       </c>
     </row>
     <row r="63" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B63" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>66.309521273648855</v>
+        <v>63.690036126164046</v>
       </c>
     </row>
     <row r="64" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B64" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>62.523738128542149</v>
+        <v>68.393102668615157</v>
       </c>
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B65" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>69.687286369623536</v>
+        <v>72.965816474382478</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B66" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>61.730907352530977</v>
+        <v>69.132891507536783</v>
       </c>
     </row>
     <row r="67" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B67" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>61.341755030029134</v>
+        <v>64.560732642842893</v>
       </c>
     </row>
     <row r="68" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B68" s="14">
         <f t="shared" ref="B68:B124" ca="1" si="3">_xlfn.NORM.INV(RAND(),66,3)</f>
-        <v>69.65492612657728</v>
+        <v>65.06553956316084</v>
       </c>
     </row>
     <row r="69" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B69" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>69.561719211726725</v>
+        <v>67.584435173268702</v>
       </c>
     </row>
     <row r="70" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B70" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>65.511879244613937</v>
+        <v>63.388505838246573</v>
       </c>
     </row>
     <row r="71" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B71" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>63.400143040605201</v>
+        <v>68.826396011148987</v>
       </c>
     </row>
     <row r="72" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B72" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>68.935900027782765</v>
+        <v>66.901953310334136</v>
       </c>
     </row>
     <row r="73" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B73" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>58.274445673974355</v>
+        <v>66.847864430089132</v>
       </c>
     </row>
     <row r="74" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B74" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>65.875412947247852</v>
+        <v>63.959480931125611</v>
       </c>
     </row>
     <row r="75" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B75" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>68.3712034609309</v>
+        <v>67.00248895781742</v>
       </c>
     </row>
     <row r="76" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B76" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>67.790685459937805</v>
+        <v>61.846276541973559</v>
       </c>
     </row>
     <row r="77" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B77" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>67.193867540338374</v>
+        <v>68.749918497984808</v>
       </c>
     </row>
     <row r="78" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B78" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>63.511825680366904</v>
+        <v>67.412689056446894</v>
       </c>
     </row>
     <row r="79" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B79" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>67.699207332452957</v>
+        <v>68.295978068811891</v>
       </c>
     </row>
     <row r="80" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B80" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>66.491354103346495</v>
+        <v>63.508756989083238</v>
       </c>
     </row>
     <row r="81" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B81" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>67.422302083424213</v>
+        <v>61.360217869183117</v>
       </c>
     </row>
     <row r="82" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B82" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>71.851338202611345</v>
+        <v>70.181761015750197</v>
       </c>
     </row>
     <row r="83" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B83" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>68.52922467858356</v>
+        <v>67.717765900309033</v>
       </c>
     </row>
     <row r="84" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B84" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>63.337405874236993</v>
+        <v>66.949422645155238</v>
       </c>
     </row>
     <row r="85" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B85" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>65.34458773689299</v>
+        <v>67.580467316864755</v>
       </c>
     </row>
     <row r="86" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B86" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>64.235810639210456</v>
+        <v>65.615480189559364</v>
       </c>
     </row>
     <row r="87" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B87" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>69.085570337652257</v>
+        <v>64.663874146530233</v>
       </c>
     </row>
     <row r="88" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B88" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>64.501702664742027</v>
+        <v>63.554668904705267</v>
       </c>
     </row>
     <row r="89" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B89" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>64.023955392929409</v>
+        <v>64.212661108492156</v>
       </c>
     </row>
     <row r="90" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B90" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>67.78337711608296</v>
+        <v>63.582420345152578</v>
       </c>
     </row>
     <row r="91" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B91" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>64.917425313046166</v>
+        <v>62.866769667379245</v>
       </c>
     </row>
     <row r="92" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B92" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>62.31059437379664</v>
+        <v>69.763586669985443</v>
       </c>
     </row>
     <row r="93" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B93" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>67.029092748141395</v>
+        <v>66.019920085971251</v>
       </c>
     </row>
     <row r="94" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B94" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>65.152264894695918</v>
+        <v>68.577897562400949</v>
       </c>
     </row>
     <row r="95" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B95" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>61.199775990691577</v>
+        <v>62.928766757172859</v>
       </c>
     </row>
     <row r="96" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B96" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>67.262455224716504</v>
+        <v>60.650378600522203</v>
       </c>
     </row>
     <row r="97" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B97" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>64.354946312367261</v>
+        <v>62.55492046456169</v>
       </c>
     </row>
     <row r="98" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B98" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>63.219410471693351</v>
+        <v>64.339837049717559</v>
       </c>
     </row>
     <row r="99" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B99" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>65.831785088530282</v>
+        <v>64.601510691071496</v>
       </c>
     </row>
     <row r="100" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B100" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>66.197320849148809</v>
+        <v>69.18219008879332</v>
       </c>
     </row>
     <row r="101" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B101" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>62.884291193572345</v>
+        <v>65.18081678544219</v>
       </c>
     </row>
     <row r="102" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B102" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>63.460679233636078</v>
+        <v>62.53000958906641</v>
       </c>
     </row>
     <row r="103" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B103" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>73.396319499285866</v>
+        <v>67.023429216239364</v>
       </c>
     </row>
     <row r="104" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B104" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>69.092637651587808</v>
+        <v>65.419694574125401</v>
       </c>
     </row>
     <row r="105" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B105" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>64.589616250500043</v>
+        <v>64.527943122945032</v>
       </c>
     </row>
     <row r="106" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B106" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>68.946282091601773</v>
+        <v>63.990051817670349</v>
       </c>
     </row>
     <row r="107" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B107" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>65.383162698307871</v>
+        <v>64.048047928929293</v>
       </c>
     </row>
     <row r="108" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B108" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>70.301066217215109</v>
+        <v>66.004054158487477</v>
       </c>
     </row>
     <row r="109" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B109" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>70.203168423284751</v>
+        <v>63.730839164069721</v>
       </c>
     </row>
     <row r="110" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B110" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>71.809462331261898</v>
+        <v>64.306882565104132</v>
       </c>
     </row>
     <row r="111" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B111" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>73.447719531860685</v>
+        <v>65.939897352211545</v>
       </c>
     </row>
     <row r="112" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B112" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>68.717819107289174</v>
+        <v>64.462662881571831</v>
       </c>
     </row>
     <row r="113" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B113" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>72.504274540477724</v>
+        <v>68.607508675355433</v>
       </c>
     </row>
     <row r="114" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B114" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>69.951422067288604</v>
+        <v>64.862267423302882</v>
       </c>
     </row>
     <row r="115" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B115" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>58.303169578667131</v>
+        <v>65.029873080459183</v>
       </c>
     </row>
     <row r="116" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B116" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>66.480416186446703</v>
+        <v>60.474622861672934</v>
       </c>
     </row>
     <row r="117" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B117" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>68.577242095825738</v>
+        <v>66.903253566519751</v>
       </c>
     </row>
     <row r="118" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B118" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>65.552419774222798</v>
+        <v>61.708456177973119</v>
       </c>
     </row>
     <row r="119" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B119" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>63.471827882930448</v>
+        <v>64.37725790007093</v>
       </c>
     </row>
     <row r="120" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B120" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>63.740992429480627</v>
+        <v>68.591284302048706</v>
       </c>
     </row>
     <row r="121" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B121" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>61.109774491819493</v>
+        <v>70.403276438005832</v>
       </c>
     </row>
     <row r="122" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B122" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>71.67991871011391</v>
+        <v>62.94308564332897</v>
       </c>
     </row>
     <row r="123" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B123" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>68.559326478881999</v>
+        <v>65.928881334843581</v>
       </c>
     </row>
     <row r="124" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B124" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>71.443183406472144</v>
+        <v>62.630583080097253</v>
       </c>
     </row>
   </sheetData>
@@ -15232,7 +15262,7 @@
     <row r="3" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="14">
         <f ca="1">'Almost Histogram'!B3</f>
-        <v>69.475439609415915</v>
+        <v>66.242934483345223</v>
       </c>
       <c r="E3" s="67"/>
       <c r="F3" s="69"/>
@@ -15241,38 +15271,38 @@
     <row r="4" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B4" s="14">
         <f ca="1">'Almost Histogram'!B4</f>
-        <v>63.616852833726099</v>
+        <v>64.733945362871481</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="38" cm="1">
         <f t="array" aca="1" ref="D4:D6" ca="1">'Almost Histogram'!D4:D6</f>
-        <v>73.447719531860685</v>
+        <v>72.965816474382478</v>
       </c>
       <c r="E4" s="13" cm="1">
         <f t="array" aca="1" ref="E4:E13" ca="1">'Almost Histogram'!E4:E13</f>
-        <v>59.9</v>
+        <v>61.599999999999994</v>
       </c>
       <c r="F4" s="14" cm="1">
         <f t="array" aca="1" ref="F4:F14" ca="1">ROUND(FREQUENCY(B3:B124,E4:E13)/D6,2)</f>
-        <v>1.88</v>
+        <v>6.15</v>
       </c>
       <c r="G4" s="12">
         <f t="shared" ref="G4:G13" ca="1" si="0">F4/COUNT(B:B)</f>
-        <v>1.540983606557377E-2</v>
+        <v>5.0409836065573775E-2</v>
       </c>
       <c r="H4" s="33">
         <f ca="1">E4-D6</f>
-        <v>58.3</v>
+        <v>60.3</v>
       </c>
       <c r="I4" s="33" cm="1">
         <f t="array" aca="1" ref="I4:I13" ca="1">'Almost Histogram'!H4:H13</f>
-        <v>59.087222836987181</v>
+        <v>60.968868572062917</v>
       </c>
       <c r="P4" s="53" t="str">
         <f ca="1">"The area of this bar is "&amp;F9&amp;"×"&amp;D6&amp;"="&amp;ROUND(D6*F9,0)&amp;" which is the frequency for this bin."</f>
-        <v>The area of this bar is 13.13×1.6=21 which is the frequency for this bin.</v>
+        <v>The area of this bar is 15.38×1.3=20 which is the frequency for this bin.</v>
       </c>
       <c r="Q4" s="54"/>
       <c r="R4" s="54"/>
@@ -15283,33 +15313,33 @@
     <row r="5" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B5" s="14">
         <f ca="1">'Almost Histogram'!B5</f>
-        <v>65.991284820702205</v>
+        <v>66.20535912179669</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="38">
         <f ca="1"/>
-        <v>58.274445673974355</v>
+        <v>60.337737144125832</v>
       </c>
       <c r="E5" s="13">
         <f ca="1"/>
-        <v>61.5</v>
+        <v>62.899999999999991</v>
       </c>
       <c r="F5" s="14">
         <f ca="1"/>
-        <v>4.38</v>
+        <v>10</v>
       </c>
       <c r="G5" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>3.5901639344262291E-2</v>
+        <v>8.1967213114754092E-2</v>
       </c>
       <c r="H5" s="33" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="33">
         <f ca="1"/>
-        <v>60.7</v>
+        <v>62.249999999999993</v>
       </c>
       <c r="P5" s="56"/>
       <c r="Q5" s="57"/>
@@ -15321,33 +15351,33 @@
     <row r="6" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="14">
         <f ca="1">'Almost Histogram'!B6</f>
-        <v>66.623824883313574</v>
+        <v>70.566312528836036</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="11">
         <f ca="1"/>
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="E6" s="13">
         <f ca="1"/>
-        <v>63.1</v>
+        <v>64.199999999999989</v>
       </c>
       <c r="F6" s="14">
         <f ca="1"/>
-        <v>5.63</v>
+        <v>13.08</v>
       </c>
       <c r="G6" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>4.6147540983606558E-2</v>
+        <v>0.10721311475409837</v>
       </c>
       <c r="H6" s="33" t="s">
         <v>24</v>
       </c>
       <c r="I6" s="33">
         <f ca="1"/>
-        <v>62.3</v>
+        <v>63.54999999999999</v>
       </c>
       <c r="P6" s="59"/>
       <c r="Q6" s="60"/>
@@ -15359,78 +15389,78 @@
     <row r="7" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B7" s="14">
         <f ca="1">'Almost Histogram'!B7</f>
-        <v>67.230278665089998</v>
+        <v>63.835344305202476</v>
       </c>
       <c r="E7" s="13">
         <f ca="1"/>
-        <v>64.7</v>
+        <v>65.499999999999986</v>
       </c>
       <c r="F7" s="14">
         <f ca="1"/>
-        <v>12.5</v>
+        <v>14.62</v>
       </c>
       <c r="G7" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>0.10245901639344263</v>
+        <v>0.11983606557377048</v>
       </c>
       <c r="H7" s="33">
         <f t="shared" ref="H7:H11" ca="1" si="1">E7-D9</f>
-        <v>64.7</v>
+        <v>65.499999999999986</v>
       </c>
       <c r="I7" s="33">
         <f ca="1"/>
-        <v>63.900000000000006</v>
+        <v>64.849999999999994</v>
       </c>
     </row>
     <row r="8" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="14">
         <f ca="1">'Almost Histogram'!B8</f>
-        <v>67.918580042523629</v>
+        <v>68.12539793235554</v>
       </c>
       <c r="E8" s="13">
         <f ca="1"/>
-        <v>66.3</v>
+        <v>66.799999999999983</v>
       </c>
       <c r="F8" s="14">
         <f ca="1"/>
-        <v>12.5</v>
+        <v>13.08</v>
       </c>
       <c r="G8" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>0.10245901639344263</v>
+        <v>0.10721311475409837</v>
       </c>
       <c r="H8" s="33" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="33">
         <f ca="1"/>
-        <v>65.5</v>
+        <v>66.149999999999977</v>
       </c>
     </row>
     <row r="9" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="14">
         <f ca="1">'Almost Histogram'!B9</f>
-        <v>66.23931331263168</v>
+        <v>70.406940346506488</v>
       </c>
       <c r="E9" s="13">
         <f ca="1"/>
-        <v>67.899999999999991</v>
+        <v>68.09999999999998</v>
       </c>
       <c r="F9" s="49">
         <f ca="1"/>
-        <v>13.13</v>
+        <v>15.38</v>
       </c>
       <c r="G9" s="50">
         <f t="shared" ca="1" si="0"/>
-        <v>0.10762295081967213</v>
+        <v>0.12606557377049182</v>
       </c>
       <c r="H9" s="33">
         <f ca="1">E9-D11</f>
-        <v>67.899999999999991</v>
+        <v>68.09999999999998</v>
       </c>
       <c r="I9" s="33">
         <f ca="1"/>
-        <v>67.099999999999994</v>
+        <v>67.449999999999989</v>
       </c>
       <c r="P9" s="53" t="s">
         <v>14</v>
@@ -15444,24 +15474,24 @@
     <row r="10" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="14">
         <f ca="1">'Almost Histogram'!B10</f>
-        <v>66.714785283063534</v>
+        <v>68.758300257521469</v>
       </c>
       <c r="E10" s="13">
         <f ca="1"/>
-        <v>69.499999999999986</v>
+        <v>69.399999999999977</v>
       </c>
       <c r="F10" s="14">
         <f ca="1"/>
-        <v>11.88</v>
+        <v>11.54</v>
       </c>
       <c r="G10" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>9.7377049180327871E-2</v>
+        <v>9.4590163934426222E-2</v>
       </c>
       <c r="H10" s="33"/>
       <c r="I10" s="33">
         <f ca="1"/>
-        <v>68.699999999999989</v>
+        <v>68.749999999999972</v>
       </c>
       <c r="P10" s="56"/>
       <c r="Q10" s="57"/>
@@ -15473,27 +15503,27 @@
     <row r="11" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="14">
         <f ca="1">'Almost Histogram'!B11</f>
-        <v>62.717326388430067</v>
+        <v>68.052733629157672</v>
       </c>
       <c r="E11" s="13">
         <f ca="1"/>
-        <v>71.09999999999998</v>
+        <v>70.699999999999974</v>
       </c>
       <c r="F11" s="14">
         <f ca="1"/>
-        <v>8.1300000000000008</v>
+        <v>7.69</v>
       </c>
       <c r="G11" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>6.6639344262295092E-2</v>
+        <v>6.3032786885245912E-2</v>
       </c>
       <c r="H11" s="33">
         <f t="shared" ca="1" si="1"/>
-        <v>71.09999999999998</v>
+        <v>70.699999999999974</v>
       </c>
       <c r="I11" s="33">
         <f ca="1"/>
-        <v>70.299999999999983</v>
+        <v>70.049999999999983</v>
       </c>
       <c r="P11" s="56"/>
       <c r="Q11" s="57"/>
@@ -15505,24 +15535,24 @@
     <row r="12" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="14">
         <f ca="1">'Almost Histogram'!B12</f>
-        <v>72.886580462744575</v>
+        <v>60.337737144125832</v>
       </c>
       <c r="E12" s="13">
         <f ca="1"/>
-        <v>72.699999999999974</v>
+        <v>71.999999999999972</v>
       </c>
       <c r="F12" s="14">
         <f ca="1"/>
-        <v>3.75</v>
+        <v>0.77</v>
       </c>
       <c r="G12" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>3.0737704918032786E-2</v>
+        <v>6.3114754098360657E-3</v>
       </c>
       <c r="H12" s="33"/>
       <c r="I12" s="33">
         <f ca="1"/>
-        <v>71.899999999999977</v>
+        <v>71.349999999999966</v>
       </c>
       <c r="P12" s="56"/>
       <c r="Q12" s="57"/>
@@ -15534,24 +15564,24 @@
     <row r="13" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="14">
         <f ca="1">'Almost Histogram'!B13</f>
-        <v>63.360895965013576</v>
+        <v>66.232521294311383</v>
       </c>
       <c r="E13" s="13">
         <f ca="1"/>
-        <v>74.299999999999969</v>
+        <v>73.299999999999969</v>
       </c>
       <c r="F13" s="14">
         <f ca="1"/>
-        <v>2.5</v>
+        <v>1.54</v>
       </c>
       <c r="G13" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>2.0491803278688523E-2</v>
+        <v>1.2622950819672131E-2</v>
       </c>
       <c r="H13" s="33"/>
       <c r="I13" s="33">
         <f ca="1"/>
-        <v>73.499999999999972</v>
+        <v>72.649999999999977</v>
       </c>
       <c r="P13" s="56"/>
       <c r="Q13" s="57"/>
@@ -15563,7 +15593,7 @@
     <row r="14" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="14">
         <f ca="1">'Almost Histogram'!B14</f>
-        <v>70.966145710318912</v>
+        <v>66.244666483025384</v>
       </c>
       <c r="F14" s="34">
         <f ca="1"/>
@@ -15571,7 +15601,7 @@
       </c>
       <c r="H14" s="33">
         <f ca="1">E13</f>
-        <v>74.299999999999969</v>
+        <v>73.299999999999969</v>
       </c>
       <c r="P14" s="56"/>
       <c r="Q14" s="57"/>
@@ -15583,7 +15613,7 @@
     <row r="15" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="14">
         <f ca="1">'Almost Histogram'!B15</f>
-        <v>66.463157399011621</v>
+        <v>72.926828735755066</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>13</v>
@@ -15594,7 +15624,7 @@
       </c>
       <c r="G15" s="32">
         <f ca="1">SUM(G4:G13)*D6</f>
-        <v>1.0003934426229508</v>
+        <v>1.0000409836065574</v>
       </c>
       <c r="P15" s="56"/>
       <c r="Q15" s="57"/>
@@ -15606,7 +15636,7 @@
     <row r="16" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="14">
         <f ca="1">'Almost Histogram'!B16</f>
-        <v>71.375758875760511</v>
+        <v>70.680988386002909</v>
       </c>
       <c r="P16" s="56"/>
       <c r="Q16" s="57"/>
@@ -15618,7 +15648,7 @@
     <row r="17" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="14">
         <f ca="1">'Almost Histogram'!B17</f>
-        <v>63.376406097747228</v>
+        <v>62.879952427261607</v>
       </c>
       <c r="P17" s="56"/>
       <c r="Q17" s="57"/>
@@ -15630,7 +15660,7 @@
     <row r="18" spans="2:21" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="14">
         <f ca="1">'Almost Histogram'!B18</f>
-        <v>68.993907295192471</v>
+        <v>66.520814865113479</v>
       </c>
       <c r="P18" s="59"/>
       <c r="Q18" s="60"/>
@@ -15642,13 +15672,13 @@
     <row r="19" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="14">
         <f ca="1">'Almost Histogram'!B19</f>
-        <v>65.121698245632544</v>
+        <v>65.799904367928704</v>
       </c>
     </row>
     <row r="20" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="14">
         <f ca="1">'Almost Histogram'!B20</f>
-        <v>67.566494777888394</v>
+        <v>63.813916334643544</v>
       </c>
       <c r="P20" s="53" t="s">
         <v>34</v>
@@ -15662,7 +15692,7 @@
     <row r="21" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="14">
         <f ca="1">'Almost Histogram'!B21</f>
-        <v>69.580088601349573</v>
+        <v>64.136402301466291</v>
       </c>
       <c r="P21" s="56"/>
       <c r="Q21" s="57"/>
@@ -15674,7 +15704,7 @@
     <row r="22" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="14">
         <f ca="1">'Almost Histogram'!B22</f>
-        <v>62.798699462229642</v>
+        <v>62.786435009059964</v>
       </c>
       <c r="P22" s="56"/>
       <c r="Q22" s="57"/>
@@ -15686,7 +15716,7 @@
     <row r="23" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="14">
         <f ca="1">'Almost Histogram'!B23</f>
-        <v>61.272925749941827</v>
+        <v>69.568648923401881</v>
       </c>
       <c r="P23" s="56"/>
       <c r="Q23" s="57"/>
@@ -15698,7 +15728,7 @@
     <row r="24" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="14">
         <f ca="1">'Almost Histogram'!B24</f>
-        <v>68.196609272025015</v>
+        <v>64.317414586693502</v>
       </c>
       <c r="P24" s="56"/>
       <c r="Q24" s="57"/>
@@ -15710,7 +15740,7 @@
     <row r="25" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="14">
         <f ca="1">'Almost Histogram'!B25</f>
-        <v>63.607069756577225</v>
+        <v>66.061558501820087</v>
       </c>
       <c r="P25" s="59"/>
       <c r="Q25" s="60"/>
@@ -15722,17 +15752,17 @@
     <row r="26" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="14">
         <f ca="1">'Almost Histogram'!B26</f>
-        <v>66.366132304135633</v>
+        <v>65.765903101851904</v>
       </c>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B27" s="14">
         <f ca="1">'Almost Histogram'!B27</f>
-        <v>68.751086314844912</v>
+        <v>66.820491715120312</v>
       </c>
       <c r="P27" s="53" t="str">
         <f ca="1">"The area of this bar is "&amp;ROUND(G9*100,2)&amp;"%×"&amp;D6&amp;"="&amp;ROUND(D6*G9*100,2)&amp;"% which is the frequency for this bin."</f>
-        <v>The area of this bar is 10.76%×1.6=17.22% which is the frequency for this bin.</v>
+        <v>The area of this bar is 12.61%×1.3=16.39% which is the frequency for this bin.</v>
       </c>
       <c r="Q27" s="54"/>
       <c r="R27" s="54"/>
@@ -15743,7 +15773,7 @@
     <row r="28" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B28" s="14">
         <f ca="1">'Almost Histogram'!B28</f>
-        <v>65.873687668860754</v>
+        <v>68.263157362157685</v>
       </c>
       <c r="P28" s="56"/>
       <c r="Q28" s="57"/>
@@ -15755,7 +15785,7 @@
     <row r="29" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="14">
         <f ca="1">'Almost Histogram'!B29</f>
-        <v>69.038928403175078</v>
+        <v>63.751664011456583</v>
       </c>
       <c r="P29" s="59"/>
       <c r="Q29" s="60"/>
@@ -15767,37 +15797,37 @@
     <row r="30" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B30" s="14">
         <f ca="1">'Almost Histogram'!B30</f>
-        <v>64.79447986422656</v>
+        <v>61.139526115604589</v>
       </c>
     </row>
     <row r="31" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B31" s="14">
         <f ca="1">'Almost Histogram'!B31</f>
-        <v>68.258326414238397</v>
+        <v>61.832624825508717</v>
       </c>
     </row>
     <row r="32" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="14">
         <f ca="1">'Almost Histogram'!B32</f>
-        <v>62.730611908912472</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>64.458155759942073</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="14">
         <f ca="1">'Almost Histogram'!B33</f>
-        <v>67.732790768257743</v>
-      </c>
-      <c r="I33" s="62" t="s">
+        <v>71.43623843106856</v>
+      </c>
+      <c r="I33" s="79" t="s">
         <v>35</v>
       </c>
-      <c r="J33" s="63"/>
-      <c r="K33" s="63"/>
-      <c r="L33" s="64"/>
+      <c r="J33" s="80"/>
+      <c r="K33" s="80"/>
+      <c r="L33" s="81"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="14">
         <f ca="1">'Almost Histogram'!B34</f>
-        <v>67.732008088296539</v>
+        <v>70.380261068021241</v>
       </c>
       <c r="I34" s="65" t="s">
         <v>36</v>
@@ -15809,541 +15839,541 @@
     <row r="35" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B35" s="14">
         <f ca="1">'Almost Histogram'!B35</f>
-        <v>66.933572867587372</v>
+        <v>67.958562513892531</v>
       </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B36" s="14">
         <f ca="1">'Almost Histogram'!B36</f>
-        <v>68.250670132527418</v>
+        <v>67.050559490969547</v>
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B37" s="14">
         <f ca="1">'Almost Histogram'!B37</f>
-        <v>59.661817353543697</v>
+        <v>67.724337352905977</v>
       </c>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B38" s="14">
         <f ca="1">'Almost Histogram'!B38</f>
-        <v>60.09508594830038</v>
+        <v>62.770845880537131</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B39" s="14">
         <f ca="1">'Almost Histogram'!B39</f>
-        <v>70.787846692610145</v>
+        <v>62.293042269721461</v>
       </c>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B40" s="14">
         <f ca="1">'Almost Histogram'!B40</f>
-        <v>69.66281205015099</v>
+        <v>65.536563806302993</v>
       </c>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B41" s="14">
         <f ca="1">'Almost Histogram'!B41</f>
-        <v>69.01873232943548</v>
+        <v>67.207745864465835</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B42" s="14">
         <f ca="1">'Almost Histogram'!B42</f>
-        <v>72.904379406546724</v>
+        <v>62.547370272693669</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B43" s="14">
         <f ca="1">'Almost Histogram'!B43</f>
-        <v>66.741820053561838</v>
+        <v>69.392140184375819</v>
       </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B44" s="14">
         <f ca="1">'Almost Histogram'!B44</f>
-        <v>65.407956382634339</v>
+        <v>67.729854637108858</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B45" s="14">
         <f ca="1">'Almost Histogram'!B45</f>
-        <v>67.248773020074722</v>
+        <v>66.083867300281312</v>
       </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B46" s="14">
         <f ca="1">'Almost Histogram'!B46</f>
-        <v>63.616341912223312</v>
+        <v>67.317733735635542</v>
       </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B47" s="14">
         <f ca="1">'Almost Histogram'!B47</f>
-        <v>66.016419424342288</v>
+        <v>66.770176536641756</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B48" s="14">
         <f ca="1">'Almost Histogram'!B48</f>
-        <v>69.57620562002127</v>
+        <v>65.802601715232484</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" s="14">
         <f ca="1">'Almost Histogram'!B49</f>
-        <v>65.660848371674192</v>
+        <v>60.686868681992188</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B50" s="14">
         <f ca="1">'Almost Histogram'!B50</f>
-        <v>62.368526769562038</v>
+        <v>70.631436966120845</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B51" s="14">
         <f ca="1">'Almost Histogram'!B51</f>
-        <v>63.234695801963049</v>
+        <v>67.822231309414491</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B52" s="14">
         <f ca="1">'Almost Histogram'!B52</f>
-        <v>69.877266762241959</v>
+        <v>65.451083517140262</v>
       </c>
     </row>
     <row r="53" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B53" s="14">
         <f ca="1">'Almost Histogram'!B53</f>
-        <v>68.614950776555119</v>
+        <v>69.889156638810135</v>
       </c>
     </row>
     <row r="54" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B54" s="14">
         <f ca="1">'Almost Histogram'!B54</f>
-        <v>60.223604529459777</v>
+        <v>62.575792941732757</v>
       </c>
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B55" s="14">
         <f ca="1">'Almost Histogram'!B55</f>
-        <v>70.803936966712754</v>
+        <v>68.790168500099284</v>
       </c>
     </row>
     <row r="56" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B56" s="14">
         <f ca="1">'Almost Histogram'!B56</f>
-        <v>65.406153874396821</v>
+        <v>65.195396415878776</v>
       </c>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B57" s="14">
         <f ca="1">'Almost Histogram'!B57</f>
-        <v>62.478361733531543</v>
+        <v>67.083526236133267</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B58" s="14">
         <f ca="1">'Almost Histogram'!B58</f>
-        <v>65.733687038141014</v>
+        <v>69.226471004443937</v>
       </c>
     </row>
     <row r="59" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B59" s="14">
         <f ca="1">'Almost Histogram'!B59</f>
-        <v>61.344876881641696</v>
+        <v>61.030827750936695</v>
       </c>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B60" s="14">
         <f ca="1">'Almost Histogram'!B60</f>
-        <v>66.240712540221054</v>
+        <v>63.986155098356939</v>
       </c>
     </row>
     <row r="61" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B61" s="14">
         <f ca="1">'Almost Histogram'!B61</f>
-        <v>64.539003450063646</v>
+        <v>63.699223418430471</v>
       </c>
     </row>
     <row r="62" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B62" s="14">
         <f ca="1">'Almost Histogram'!B62</f>
-        <v>64.106198254993345</v>
+        <v>60.524657455882306</v>
       </c>
     </row>
     <row r="63" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B63" s="14">
         <f ca="1">'Almost Histogram'!B63</f>
-        <v>66.309521273648855</v>
+        <v>63.690036126164046</v>
       </c>
     </row>
     <row r="64" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B64" s="14">
         <f ca="1">'Almost Histogram'!B64</f>
-        <v>62.523738128542149</v>
+        <v>68.393102668615157</v>
       </c>
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B65" s="14">
         <f ca="1">'Almost Histogram'!B65</f>
-        <v>69.687286369623536</v>
+        <v>72.965816474382478</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B66" s="14">
         <f ca="1">'Almost Histogram'!B66</f>
-        <v>61.730907352530977</v>
+        <v>69.132891507536783</v>
       </c>
     </row>
     <row r="67" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B67" s="14">
         <f ca="1">'Almost Histogram'!B67</f>
-        <v>61.341755030029134</v>
+        <v>64.560732642842893</v>
       </c>
     </row>
     <row r="68" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B68" s="14">
         <f ca="1">'Almost Histogram'!B68</f>
-        <v>69.65492612657728</v>
+        <v>65.06553956316084</v>
       </c>
     </row>
     <row r="69" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B69" s="14">
         <f ca="1">'Almost Histogram'!B69</f>
-        <v>69.561719211726725</v>
+        <v>67.584435173268702</v>
       </c>
     </row>
     <row r="70" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B70" s="14">
         <f ca="1">'Almost Histogram'!B70</f>
-        <v>65.511879244613937</v>
+        <v>63.388505838246573</v>
       </c>
     </row>
     <row r="71" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B71" s="14">
         <f ca="1">'Almost Histogram'!B71</f>
-        <v>63.400143040605201</v>
+        <v>68.826396011148987</v>
       </c>
     </row>
     <row r="72" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B72" s="14">
         <f ca="1">'Almost Histogram'!B72</f>
-        <v>68.935900027782765</v>
+        <v>66.901953310334136</v>
       </c>
     </row>
     <row r="73" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B73" s="14">
         <f ca="1">'Almost Histogram'!B73</f>
-        <v>58.274445673974355</v>
+        <v>66.847864430089132</v>
       </c>
     </row>
     <row r="74" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B74" s="14">
         <f ca="1">'Almost Histogram'!B74</f>
-        <v>65.875412947247852</v>
+        <v>63.959480931125611</v>
       </c>
     </row>
     <row r="75" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B75" s="14">
         <f ca="1">'Almost Histogram'!B75</f>
-        <v>68.3712034609309</v>
+        <v>67.00248895781742</v>
       </c>
     </row>
     <row r="76" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B76" s="14">
         <f ca="1">'Almost Histogram'!B76</f>
-        <v>67.790685459937805</v>
+        <v>61.846276541973559</v>
       </c>
     </row>
     <row r="77" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B77" s="14">
         <f ca="1">'Almost Histogram'!B77</f>
-        <v>67.193867540338374</v>
+        <v>68.749918497984808</v>
       </c>
     </row>
     <row r="78" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B78" s="14">
         <f ca="1">'Almost Histogram'!B78</f>
-        <v>63.511825680366904</v>
+        <v>67.412689056446894</v>
       </c>
     </row>
     <row r="79" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B79" s="14">
         <f ca="1">'Almost Histogram'!B79</f>
-        <v>67.699207332452957</v>
+        <v>68.295978068811891</v>
       </c>
     </row>
     <row r="80" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B80" s="14">
         <f ca="1">'Almost Histogram'!B80</f>
-        <v>66.491354103346495</v>
+        <v>63.508756989083238</v>
       </c>
     </row>
     <row r="81" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B81" s="14">
         <f ca="1">'Almost Histogram'!B81</f>
-        <v>67.422302083424213</v>
+        <v>61.360217869183117</v>
       </c>
     </row>
     <row r="82" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B82" s="14">
         <f ca="1">'Almost Histogram'!B82</f>
-        <v>71.851338202611345</v>
+        <v>70.181761015750197</v>
       </c>
     </row>
     <row r="83" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B83" s="14">
         <f ca="1">'Almost Histogram'!B83</f>
-        <v>68.52922467858356</v>
+        <v>67.717765900309033</v>
       </c>
     </row>
     <row r="84" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B84" s="14">
         <f ca="1">'Almost Histogram'!B84</f>
-        <v>63.337405874236993</v>
+        <v>66.949422645155238</v>
       </c>
     </row>
     <row r="85" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B85" s="14">
         <f ca="1">'Almost Histogram'!B85</f>
-        <v>65.34458773689299</v>
+        <v>67.580467316864755</v>
       </c>
     </row>
     <row r="86" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B86" s="14">
         <f ca="1">'Almost Histogram'!B86</f>
-        <v>64.235810639210456</v>
+        <v>65.615480189559364</v>
       </c>
     </row>
     <row r="87" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B87" s="14">
         <f ca="1">'Almost Histogram'!B87</f>
-        <v>69.085570337652257</v>
+        <v>64.663874146530233</v>
       </c>
     </row>
     <row r="88" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B88" s="14">
         <f ca="1">'Almost Histogram'!B88</f>
-        <v>64.501702664742027</v>
+        <v>63.554668904705267</v>
       </c>
     </row>
     <row r="89" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B89" s="14">
         <f ca="1">'Almost Histogram'!B89</f>
-        <v>64.023955392929409</v>
+        <v>64.212661108492156</v>
       </c>
     </row>
     <row r="90" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B90" s="14">
         <f ca="1">'Almost Histogram'!B90</f>
-        <v>67.78337711608296</v>
+        <v>63.582420345152578</v>
       </c>
     </row>
     <row r="91" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B91" s="14">
         <f ca="1">'Almost Histogram'!B91</f>
-        <v>64.917425313046166</v>
+        <v>62.866769667379245</v>
       </c>
     </row>
     <row r="92" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B92" s="14">
         <f ca="1">'Almost Histogram'!B92</f>
-        <v>62.31059437379664</v>
+        <v>69.763586669985443</v>
       </c>
     </row>
     <row r="93" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B93" s="14">
         <f ca="1">'Almost Histogram'!B93</f>
-        <v>67.029092748141395</v>
+        <v>66.019920085971251</v>
       </c>
     </row>
     <row r="94" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B94" s="14">
         <f ca="1">'Almost Histogram'!B94</f>
-        <v>65.152264894695918</v>
+        <v>68.577897562400949</v>
       </c>
     </row>
     <row r="95" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B95" s="14">
         <f ca="1">'Almost Histogram'!B95</f>
-        <v>61.199775990691577</v>
+        <v>62.928766757172859</v>
       </c>
     </row>
     <row r="96" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B96" s="14">
         <f ca="1">'Almost Histogram'!B96</f>
-        <v>67.262455224716504</v>
+        <v>60.650378600522203</v>
       </c>
     </row>
     <row r="97" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B97" s="14">
         <f ca="1">'Almost Histogram'!B97</f>
-        <v>64.354946312367261</v>
+        <v>62.55492046456169</v>
       </c>
     </row>
     <row r="98" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B98" s="14">
         <f ca="1">'Almost Histogram'!B98</f>
-        <v>63.219410471693351</v>
+        <v>64.339837049717559</v>
       </c>
     </row>
     <row r="99" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B99" s="14">
         <f ca="1">'Almost Histogram'!B99</f>
-        <v>65.831785088530282</v>
+        <v>64.601510691071496</v>
       </c>
     </row>
     <row r="100" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B100" s="14">
         <f ca="1">'Almost Histogram'!B100</f>
-        <v>66.197320849148809</v>
+        <v>69.18219008879332</v>
       </c>
     </row>
     <row r="101" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B101" s="14">
         <f ca="1">'Almost Histogram'!B101</f>
-        <v>62.884291193572345</v>
+        <v>65.18081678544219</v>
       </c>
     </row>
     <row r="102" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B102" s="14">
         <f ca="1">'Almost Histogram'!B102</f>
-        <v>63.460679233636078</v>
+        <v>62.53000958906641</v>
       </c>
     </row>
     <row r="103" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B103" s="14">
         <f ca="1">'Almost Histogram'!B103</f>
-        <v>73.396319499285866</v>
+        <v>67.023429216239364</v>
       </c>
     </row>
     <row r="104" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B104" s="14">
         <f ca="1">'Almost Histogram'!B104</f>
-        <v>69.092637651587808</v>
+        <v>65.419694574125401</v>
       </c>
     </row>
     <row r="105" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B105" s="14">
         <f ca="1">'Almost Histogram'!B105</f>
-        <v>64.589616250500043</v>
+        <v>64.527943122945032</v>
       </c>
     </row>
     <row r="106" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B106" s="14">
         <f ca="1">'Almost Histogram'!B106</f>
-        <v>68.946282091601773</v>
+        <v>63.990051817670349</v>
       </c>
     </row>
     <row r="107" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B107" s="14">
         <f ca="1">'Almost Histogram'!B107</f>
-        <v>65.383162698307871</v>
+        <v>64.048047928929293</v>
       </c>
     </row>
     <row r="108" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B108" s="14">
         <f ca="1">'Almost Histogram'!B108</f>
-        <v>70.301066217215109</v>
+        <v>66.004054158487477</v>
       </c>
     </row>
     <row r="109" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B109" s="14">
         <f ca="1">'Almost Histogram'!B109</f>
-        <v>70.203168423284751</v>
+        <v>63.730839164069721</v>
       </c>
     </row>
     <row r="110" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B110" s="14">
         <f ca="1">'Almost Histogram'!B110</f>
-        <v>71.809462331261898</v>
+        <v>64.306882565104132</v>
       </c>
     </row>
     <row r="111" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B111" s="14">
         <f ca="1">'Almost Histogram'!B111</f>
-        <v>73.447719531860685</v>
+        <v>65.939897352211545</v>
       </c>
     </row>
     <row r="112" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B112" s="14">
         <f ca="1">'Almost Histogram'!B112</f>
-        <v>68.717819107289174</v>
+        <v>64.462662881571831</v>
       </c>
     </row>
     <row r="113" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B113" s="14">
         <f ca="1">'Almost Histogram'!B113</f>
-        <v>72.504274540477724</v>
+        <v>68.607508675355433</v>
       </c>
     </row>
     <row r="114" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B114" s="14">
         <f ca="1">'Almost Histogram'!B114</f>
-        <v>69.951422067288604</v>
+        <v>64.862267423302882</v>
       </c>
     </row>
     <row r="115" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B115" s="14">
         <f ca="1">'Almost Histogram'!B115</f>
-        <v>58.303169578667131</v>
+        <v>65.029873080459183</v>
       </c>
     </row>
     <row r="116" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B116" s="14">
         <f ca="1">'Almost Histogram'!B116</f>
-        <v>66.480416186446703</v>
+        <v>60.474622861672934</v>
       </c>
     </row>
     <row r="117" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B117" s="14">
         <f ca="1">'Almost Histogram'!B117</f>
-        <v>68.577242095825738</v>
+        <v>66.903253566519751</v>
       </c>
     </row>
     <row r="118" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B118" s="14">
         <f ca="1">'Almost Histogram'!B118</f>
-        <v>65.552419774222798</v>
+        <v>61.708456177973119</v>
       </c>
     </row>
     <row r="119" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B119" s="14">
         <f ca="1">'Almost Histogram'!B119</f>
-        <v>63.471827882930448</v>
+        <v>64.37725790007093</v>
       </c>
     </row>
     <row r="120" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B120" s="14">
         <f ca="1">'Almost Histogram'!B120</f>
-        <v>63.740992429480627</v>
+        <v>68.591284302048706</v>
       </c>
     </row>
     <row r="121" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B121" s="14">
         <f ca="1">'Almost Histogram'!B121</f>
-        <v>61.109774491819493</v>
+        <v>70.403276438005832</v>
       </c>
     </row>
     <row r="122" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B122" s="14">
         <f ca="1">'Almost Histogram'!B122</f>
-        <v>71.67991871011391</v>
+        <v>62.94308564332897</v>
       </c>
     </row>
     <row r="123" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B123" s="14">
         <f ca="1">'Almost Histogram'!B123</f>
-        <v>68.559326478881999</v>
+        <v>65.928881334843581</v>
       </c>
     </row>
     <row r="124" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B124" s="14">
         <f ca="1">'Almost Histogram'!B124</f>
-        <v>71.443183406472144</v>
+        <v>62.630583080097253</v>
       </c>
     </row>
   </sheetData>
@@ -16401,7 +16431,7 @@
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="14">
         <f ca="1">'Almost Histogram'!B3</f>
-        <v>69.475439609415915</v>
+        <v>66.242934483345223</v>
       </c>
       <c r="C3" s="31">
         <v>0</v>
@@ -16414,107 +16444,107 @@
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="14">
         <f ca="1">'Almost Histogram'!B4</f>
-        <v>63.616852833726099</v>
+        <v>64.733945362871481</v>
       </c>
       <c r="C4" s="31">
         <v>0</v>
       </c>
       <c r="D4" s="4">
         <f ca="1">'Histogram (Equal Bin Width)'!E6</f>
-        <v>63.1</v>
+        <v>64.199999999999989</v>
       </c>
       <c r="E4" s="5">
         <f t="array" aca="1" ref="E4:E7" ca="1">FREQUENCY(B:B,D4:D6)</f>
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F4" s="4">
         <f ca="1">D4-E9</f>
-        <v>4.8000000000000043</v>
+        <v>3.8999999999999915</v>
       </c>
       <c r="G4" s="14">
         <f ca="1">E4/F4</f>
-        <v>3.9583333333333299</v>
+        <v>9.743589743589764</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="14">
         <f ca="1">'Almost Histogram'!B5</f>
-        <v>65.991284820702205</v>
+        <v>66.20535912179669</v>
       </c>
       <c r="C5" s="31">
         <v>0</v>
       </c>
       <c r="D5" s="4">
         <f ca="1">'Histogram (Equal Bin Width)'!E8</f>
-        <v>66.3</v>
+        <v>66.799999999999983</v>
       </c>
       <c r="E5" s="4">
         <f ca="1"/>
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F5" s="4">
         <f ca="1">D5-D4</f>
-        <v>3.1999999999999957</v>
+        <v>2.5999999999999943</v>
       </c>
       <c r="G5" s="14">
         <f t="shared" ref="G5:G7" ca="1" si="0">E5/F5</f>
-        <v>12.500000000000016</v>
+        <v>13.846153846153877</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="14">
         <f ca="1">'Almost Histogram'!B6</f>
-        <v>66.623824883313574</v>
+        <v>70.566312528836036</v>
       </c>
       <c r="C6" s="31">
         <v>0</v>
       </c>
       <c r="D6" s="4">
         <f ca="1">'Histogram (Equal Bin Width)'!E10</f>
-        <v>69.499999999999986</v>
+        <v>69.399999999999977</v>
       </c>
       <c r="E6" s="4">
         <f ca="1"/>
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F6" s="4">
         <f ca="1">D6-D5</f>
-        <v>3.1999999999999886</v>
+        <v>2.5999999999999943</v>
       </c>
       <c r="G6" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>12.500000000000044</v>
+        <v>13.46153846153849</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="14">
         <f ca="1">'Almost Histogram'!B7</f>
-        <v>67.230278665089998</v>
+        <v>63.835344305202476</v>
       </c>
       <c r="C7" s="31">
         <v>0</v>
       </c>
       <c r="D7" s="4">
         <f ca="1">'Histogram (Equal Bin Width)'!E13</f>
-        <v>74.299999999999969</v>
+        <v>73.299999999999969</v>
       </c>
       <c r="E7" s="4">
         <f ca="1"/>
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F7" s="4">
         <f ca="1">D7-D6</f>
-        <v>4.7999999999999829</v>
+        <v>3.8999999999999915</v>
       </c>
       <c r="G7" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>4.7916666666666838</v>
+        <v>3.3333333333333406</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="14">
         <f ca="1">'Almost Histogram'!B8</f>
-        <v>67.918580042523629</v>
+        <v>68.12539793235554</v>
       </c>
       <c r="C8" s="31">
         <v>0</v>
@@ -16523,7 +16553,7 @@
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="14">
         <f ca="1">'Almost Histogram'!B9</f>
-        <v>66.23931331263168</v>
+        <v>70.406940346506488</v>
       </c>
       <c r="C9" s="31">
         <v>0</v>
@@ -16533,7 +16563,7 @@
       </c>
       <c r="E9" s="17">
         <f ca="1">ROUND('Almost Histogram'!D5,1)</f>
-        <v>58.3</v>
+        <v>60.3</v>
       </c>
       <c r="F9" s="18">
         <v>0</v>
@@ -16542,7 +16572,7 @@
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="14">
         <f ca="1">'Almost Histogram'!B10</f>
-        <v>66.714785283063534</v>
+        <v>68.758300257521469</v>
       </c>
       <c r="C10" s="31">
         <v>0</v>
@@ -16550,17 +16580,17 @@
       <c r="D10" s="19"/>
       <c r="E10" s="6">
         <f ca="1">E9</f>
-        <v>58.3</v>
+        <v>60.3</v>
       </c>
       <c r="F10" s="20">
         <f ca="1">G4</f>
-        <v>3.9583333333333299</v>
+        <v>9.743589743589764</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="14">
         <f ca="1">'Almost Histogram'!B11</f>
-        <v>62.717326388430067</v>
+        <v>68.052733629157672</v>
       </c>
       <c r="C11" s="31">
         <v>0</v>
@@ -16568,17 +16598,17 @@
       <c r="D11" s="19"/>
       <c r="E11" s="6">
         <f ca="1">(E10+E12)/2</f>
-        <v>60.7</v>
+        <v>62.249999999999993</v>
       </c>
       <c r="F11" s="20">
         <f ca="1">F10</f>
-        <v>3.9583333333333299</v>
+        <v>9.743589743589764</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="14">
         <f ca="1">'Almost Histogram'!B12</f>
-        <v>72.886580462744575</v>
+        <v>60.337737144125832</v>
       </c>
       <c r="C12" s="31">
         <v>0</v>
@@ -16586,17 +16616,17 @@
       <c r="D12" s="19"/>
       <c r="E12" s="6">
         <f ca="1">D4</f>
-        <v>63.1</v>
+        <v>64.199999999999989</v>
       </c>
       <c r="F12" s="20">
         <f ca="1">G4</f>
-        <v>3.9583333333333299</v>
+        <v>9.743589743589764</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="14">
         <f ca="1">'Almost Histogram'!B13</f>
-        <v>63.360895965013576</v>
+        <v>66.232521294311383</v>
       </c>
       <c r="C13" s="31">
         <v>0</v>
@@ -16606,7 +16636,7 @@
       </c>
       <c r="E13" s="6">
         <f ca="1">D4</f>
-        <v>63.1</v>
+        <v>64.199999999999989</v>
       </c>
       <c r="F13" s="20">
         <v>0</v>
@@ -16615,7 +16645,7 @@
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="14">
         <f ca="1">'Almost Histogram'!B14</f>
-        <v>70.966145710318912</v>
+        <v>66.244666483025384</v>
       </c>
       <c r="C14" s="31">
         <v>0</v>
@@ -16625,7 +16655,7 @@
       </c>
       <c r="E14" s="7">
         <f ca="1">D4</f>
-        <v>63.1</v>
+        <v>64.199999999999989</v>
       </c>
       <c r="F14" s="23">
         <v>0</v>
@@ -16634,7 +16664,7 @@
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="14">
         <f ca="1">'Almost Histogram'!B15</f>
-        <v>66.463157399011621</v>
+        <v>72.926828735755066</v>
       </c>
       <c r="C15" s="31">
         <v>0</v>
@@ -16644,17 +16674,17 @@
       </c>
       <c r="E15" s="7">
         <f ca="1">D4</f>
-        <v>63.1</v>
+        <v>64.199999999999989</v>
       </c>
       <c r="F15" s="23">
         <f ca="1">G5</f>
-        <v>12.500000000000016</v>
+        <v>13.846153846153877</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="14">
         <f ca="1">'Almost Histogram'!B16</f>
-        <v>71.375758875760511</v>
+        <v>70.680988386002909</v>
       </c>
       <c r="C16" s="31">
         <v>0</v>
@@ -16662,17 +16692,17 @@
       <c r="D16" s="22"/>
       <c r="E16" s="7">
         <f ca="1">(E15+E17)/2</f>
-        <v>64.7</v>
+        <v>65.499999999999986</v>
       </c>
       <c r="F16" s="23">
         <f ca="1">F15</f>
-        <v>12.500000000000016</v>
+        <v>13.846153846153877</v>
       </c>
     </row>
     <row r="17" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="14">
         <f ca="1">'Almost Histogram'!B17</f>
-        <v>63.376406097747228</v>
+        <v>62.879952427261607</v>
       </c>
       <c r="C17" s="31">
         <v>0</v>
@@ -16680,17 +16710,17 @@
       <c r="D17" s="22"/>
       <c r="E17" s="7">
         <f ca="1">D5</f>
-        <v>66.3</v>
+        <v>66.799999999999983</v>
       </c>
       <c r="F17" s="23">
         <f ca="1">G5</f>
-        <v>12.500000000000016</v>
+        <v>13.846153846153877</v>
       </c>
     </row>
     <row r="18" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="14">
         <f ca="1">'Almost Histogram'!B18</f>
-        <v>68.993907295192471</v>
+        <v>66.520814865113479</v>
       </c>
       <c r="C18" s="31">
         <v>0</v>
@@ -16700,7 +16730,7 @@
       </c>
       <c r="E18" s="7">
         <f ca="1">D5</f>
-        <v>66.3</v>
+        <v>66.799999999999983</v>
       </c>
       <c r="F18" s="23">
         <v>0</v>
@@ -16714,8 +16744,8 @@
       <c r="M18" s="55"/>
       <c r="P18" s="70" t="str" cm="1">
         <f t="array" aca="1" ref="P18" ca="1">"For comparison here is the histogram for the same data with equal bin widths. The first three bins of this are combined into a single bin in the histogram to the left. The binwidth is "&amp;'Histogram (Equal Bin Width)'!D6&amp;":"&amp;CHAR(10)&amp;'Histogram (Equal Bin Width)'!$F$4&amp;"×"&amp;'Histogram (Equal Bin Width)'!$D$6&amp;"+"&amp;'Histogram (Equal Bin Width)'!$F$5&amp;"×"&amp;'Histogram (Equal Bin Width)'!$D$6&amp;"+"&amp;'Histogram (Equal Bin Width)'!$F$6&amp;"×"&amp;'Histogram (Equal Bin Width)'!$D$6&amp;"="&amp;ROUND(SUM('Histogram (Equal Bin Width)'!F4:F6*'Histogram (Equal Bin Width)'!D6),0)</f>
-        <v>For comparison here is the histogram for the same data with equal bin widths. The first three bins of this are combined into a single bin in the histogram to the left. The binwidth is 1.6:
-1.88×1.6+4.38×1.6+5.63×1.6=19</v>
+        <v>For comparison here is the histogram for the same data with equal bin widths. The first three bins of this are combined into a single bin in the histogram to the left. The binwidth is 1.3:
+6.15×1.3+10×1.3+13.08×1.3=38</v>
       </c>
       <c r="Q18" s="71"/>
       <c r="R18" s="71"/>
@@ -16726,7 +16756,7 @@
     <row r="19" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="14">
         <f ca="1">'Almost Histogram'!B19</f>
-        <v>65.121698245632544</v>
+        <v>65.799904367928704</v>
       </c>
       <c r="C19" s="31">
         <v>0</v>
@@ -16736,7 +16766,7 @@
       </c>
       <c r="E19" s="8">
         <f ca="1">D5</f>
-        <v>66.3</v>
+        <v>66.799999999999983</v>
       </c>
       <c r="F19" s="25">
         <v>0</v>
@@ -16756,7 +16786,7 @@
     <row r="20" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="14">
         <f ca="1">'Almost Histogram'!B20</f>
-        <v>67.566494777888394</v>
+        <v>63.813916334643544</v>
       </c>
       <c r="C20" s="31">
         <v>0</v>
@@ -16764,11 +16794,11 @@
       <c r="D20" s="24"/>
       <c r="E20" s="8">
         <f ca="1">D5</f>
-        <v>66.3</v>
+        <v>66.799999999999983</v>
       </c>
       <c r="F20" s="25">
         <f ca="1">G6</f>
-        <v>12.500000000000044</v>
+        <v>13.46153846153849</v>
       </c>
       <c r="I20" s="56"/>
       <c r="J20" s="57"/>
@@ -16785,7 +16815,7 @@
     <row r="21" spans="2:21" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="14">
         <f ca="1">'Almost Histogram'!B21</f>
-        <v>69.580088601349573</v>
+        <v>64.136402301466291</v>
       </c>
       <c r="C21" s="31">
         <v>0</v>
@@ -16793,11 +16823,11 @@
       <c r="D21" s="24"/>
       <c r="E21" s="8">
         <f ca="1">(E20+E22)/2</f>
-        <v>67.899999999999991</v>
+        <v>68.09999999999998</v>
       </c>
       <c r="F21" s="25">
         <f ca="1">F20</f>
-        <v>12.500000000000044</v>
+        <v>13.46153846153849</v>
       </c>
       <c r="I21" s="59"/>
       <c r="J21" s="60"/>
@@ -16814,7 +16844,7 @@
     <row r="22" spans="2:21" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="14">
         <f ca="1">'Almost Histogram'!B22</f>
-        <v>62.798699462229642</v>
+        <v>62.786435009059964</v>
       </c>
       <c r="C22" s="31">
         <v>0</v>
@@ -16822,11 +16852,11 @@
       <c r="D22" s="24"/>
       <c r="E22" s="8">
         <f ca="1">D6</f>
-        <v>69.499999999999986</v>
+        <v>69.399999999999977</v>
       </c>
       <c r="F22" s="25">
         <f ca="1">G6</f>
-        <v>12.500000000000044</v>
+        <v>13.46153846153849</v>
       </c>
       <c r="P22" s="73"/>
       <c r="Q22" s="74"/>
@@ -16838,7 +16868,7 @@
     <row r="23" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B23" s="14">
         <f ca="1">'Almost Histogram'!B23</f>
-        <v>61.272925749941827</v>
+        <v>69.568648923401881</v>
       </c>
       <c r="C23" s="31">
         <v>0</v>
@@ -16848,14 +16878,14 @@
       </c>
       <c r="E23" s="8">
         <f ca="1">D6</f>
-        <v>69.499999999999986</v>
+        <v>69.399999999999977</v>
       </c>
       <c r="F23" s="25">
         <v>0</v>
       </c>
       <c r="H23" s="70" t="str">
         <f ca="1">"Note here that the height of a bar is now the frequency density, in this case the first bar has height "&amp;ROUND(G4,1)&amp;" and a width of "&amp;ROUND(F4,2)&amp;" for a frequency of "&amp;ROUND(G4,1)&amp;"×"&amp;ROUND(F4,2)&amp;" ≈ "&amp;ROUND(F4*G4,1)&amp;"."</f>
-        <v>Note here that the height of a bar is now the frequency density, in this case the first bar has height 4 and a width of 4.8 for a frequency of 4×4.8 ≈ 19.</v>
+        <v>Note here that the height of a bar is now the frequency density, in this case the first bar has height 9.7 and a width of 3.9 for a frequency of 9.7×3.9 ≈ 38.</v>
       </c>
       <c r="I23" s="71"/>
       <c r="J23" s="71"/>
@@ -16873,7 +16903,7 @@
     <row r="24" spans="2:21" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="14">
         <f ca="1">'Almost Histogram'!B24</f>
-        <v>68.196609272025015</v>
+        <v>64.317414586693502</v>
       </c>
       <c r="C24" s="31">
         <v>0</v>
@@ -16883,7 +16913,7 @@
       </c>
       <c r="E24" s="9">
         <f ca="1">D6</f>
-        <v>69.499999999999986</v>
+        <v>69.399999999999977</v>
       </c>
       <c r="F24" s="27">
         <v>0</v>
@@ -16905,7 +16935,7 @@
     <row r="25" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="14">
         <f ca="1">'Almost Histogram'!B25</f>
-        <v>63.607069756577225</v>
+        <v>66.061558501820087</v>
       </c>
       <c r="C25" s="31">
         <v>0</v>
@@ -16913,11 +16943,11 @@
       <c r="D25" s="26"/>
       <c r="E25" s="9">
         <f ca="1">D6</f>
-        <v>69.499999999999986</v>
+        <v>69.399999999999977</v>
       </c>
       <c r="F25" s="27">
         <f ca="1">G7</f>
-        <v>4.7916666666666838</v>
+        <v>3.3333333333333406</v>
       </c>
       <c r="H25" s="73"/>
       <c r="I25" s="74"/>
@@ -16930,7 +16960,7 @@
     <row r="26" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="14">
         <f ca="1">'Almost Histogram'!B26</f>
-        <v>66.366132304135633</v>
+        <v>65.765903101851904</v>
       </c>
       <c r="C26" s="31">
         <v>0</v>
@@ -16938,11 +16968,11 @@
       <c r="D26" s="26"/>
       <c r="E26" s="9">
         <f ca="1">(E25+E27)/2</f>
-        <v>71.899999999999977</v>
+        <v>71.349999999999966</v>
       </c>
       <c r="F26" s="27">
         <f ca="1">F25</f>
-        <v>4.7916666666666838</v>
+        <v>3.3333333333333406</v>
       </c>
       <c r="H26" s="73"/>
       <c r="I26" s="74"/>
@@ -16955,7 +16985,7 @@
     <row r="27" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="14">
         <f ca="1">'Almost Histogram'!B27</f>
-        <v>68.751086314844912</v>
+        <v>66.820491715120312</v>
       </c>
       <c r="C27" s="31">
         <v>0</v>
@@ -16963,11 +16993,11 @@
       <c r="D27" s="26"/>
       <c r="E27" s="9">
         <f ca="1">D7</f>
-        <v>74.299999999999969</v>
+        <v>73.299999999999969</v>
       </c>
       <c r="F27" s="27">
         <f ca="1">G7</f>
-        <v>4.7916666666666838</v>
+        <v>3.3333333333333406</v>
       </c>
       <c r="H27" s="76"/>
       <c r="I27" s="77"/>
@@ -16980,7 +17010,7 @@
     <row r="28" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="14">
         <f ca="1">'Almost Histogram'!B28</f>
-        <v>65.873687668860754</v>
+        <v>68.263157362157685</v>
       </c>
       <c r="C28" s="31">
         <v>0</v>
@@ -16990,7 +17020,7 @@
       </c>
       <c r="E28" s="29">
         <f ca="1">D7</f>
-        <v>74.299999999999969</v>
+        <v>73.299999999999969</v>
       </c>
       <c r="F28" s="30">
         <v>0</v>
@@ -16999,31 +17029,31 @@
     <row r="29" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="14">
         <f ca="1">'Almost Histogram'!B29</f>
-        <v>69.038928403175078</v>
+        <v>63.751664011456583</v>
       </c>
       <c r="C29" s="31">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="14">
         <f ca="1">'Almost Histogram'!B30</f>
-        <v>64.79447986422656</v>
+        <v>61.139526115604589</v>
       </c>
       <c r="C30" s="31">
         <v>0</v>
       </c>
-      <c r="I30" s="62" t="s">
+      <c r="I30" s="79" t="s">
         <v>35</v>
       </c>
-      <c r="J30" s="63"/>
-      <c r="K30" s="63"/>
-      <c r="L30" s="64"/>
+      <c r="J30" s="80"/>
+      <c r="K30" s="80"/>
+      <c r="L30" s="81"/>
     </row>
     <row r="31" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B31" s="14">
         <f ca="1">'Almost Histogram'!B31</f>
-        <v>68.258326414238397</v>
+        <v>61.832624825508717</v>
       </c>
       <c r="C31" s="31">
         <v>0</v>
@@ -17038,7 +17068,7 @@
     <row r="32" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B32" s="14">
         <f ca="1">'Almost Histogram'!B32</f>
-        <v>62.730611908912472</v>
+        <v>64.458155759942073</v>
       </c>
       <c r="C32" s="31">
         <v>0</v>
@@ -17047,7 +17077,7 @@
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="14">
         <f ca="1">'Almost Histogram'!B33</f>
-        <v>67.732790768257743</v>
+        <v>71.43623843106856</v>
       </c>
       <c r="C33" s="31">
         <v>0</v>
@@ -17056,7 +17086,7 @@
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="14">
         <f ca="1">'Almost Histogram'!B34</f>
-        <v>67.732008088296539</v>
+        <v>70.380261068021241</v>
       </c>
       <c r="C34" s="31">
         <v>0</v>
@@ -17065,7 +17095,7 @@
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="14">
         <f ca="1">'Almost Histogram'!B35</f>
-        <v>66.933572867587372</v>
+        <v>67.958562513892531</v>
       </c>
       <c r="C35" s="31">
         <v>0</v>
@@ -17074,7 +17104,7 @@
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="14">
         <f ca="1">'Almost Histogram'!B36</f>
-        <v>68.250670132527418</v>
+        <v>67.050559490969547</v>
       </c>
       <c r="C36" s="31">
         <v>0</v>
@@ -17083,7 +17113,7 @@
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="14">
         <f ca="1">'Almost Histogram'!B37</f>
-        <v>59.661817353543697</v>
+        <v>67.724337352905977</v>
       </c>
       <c r="C37" s="31">
         <v>0</v>
@@ -17092,7 +17122,7 @@
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="14">
         <f ca="1">'Almost Histogram'!B38</f>
-        <v>60.09508594830038</v>
+        <v>62.770845880537131</v>
       </c>
       <c r="C38" s="31">
         <v>0</v>
@@ -17101,7 +17131,7 @@
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="14">
         <f ca="1">'Almost Histogram'!B39</f>
-        <v>70.787846692610145</v>
+        <v>62.293042269721461</v>
       </c>
       <c r="C39" s="31">
         <v>0</v>
@@ -17110,7 +17140,7 @@
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="14">
         <f ca="1">'Almost Histogram'!B40</f>
-        <v>69.66281205015099</v>
+        <v>65.536563806302993</v>
       </c>
       <c r="C40" s="31">
         <v>0</v>
@@ -17119,7 +17149,7 @@
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="14">
         <f ca="1">'Almost Histogram'!B41</f>
-        <v>69.01873232943548</v>
+        <v>67.207745864465835</v>
       </c>
       <c r="C41" s="31">
         <v>0</v>
@@ -17128,7 +17158,7 @@
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="14">
         <f ca="1">'Almost Histogram'!B42</f>
-        <v>72.904379406546724</v>
+        <v>62.547370272693669</v>
       </c>
       <c r="C42" s="31">
         <v>0</v>
@@ -17137,7 +17167,7 @@
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="14">
         <f ca="1">'Almost Histogram'!B43</f>
-        <v>66.741820053561838</v>
+        <v>69.392140184375819</v>
       </c>
       <c r="C43" s="31">
         <v>0</v>
@@ -17146,7 +17176,7 @@
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" s="14">
         <f ca="1">'Almost Histogram'!B44</f>
-        <v>65.407956382634339</v>
+        <v>67.729854637108858</v>
       </c>
       <c r="C44" s="31">
         <v>0</v>
@@ -17155,7 +17185,7 @@
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" s="14">
         <f ca="1">'Almost Histogram'!B45</f>
-        <v>67.248773020074722</v>
+        <v>66.083867300281312</v>
       </c>
       <c r="C45" s="31">
         <v>0</v>
@@ -17164,7 +17194,7 @@
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="14">
         <f ca="1">'Almost Histogram'!B46</f>
-        <v>63.616341912223312</v>
+        <v>67.317733735635542</v>
       </c>
       <c r="C46" s="31">
         <v>0</v>
@@ -17173,7 +17203,7 @@
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="14">
         <f ca="1">'Almost Histogram'!B47</f>
-        <v>66.016419424342288</v>
+        <v>66.770176536641756</v>
       </c>
       <c r="C47" s="31">
         <v>0</v>
@@ -17182,7 +17212,7 @@
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="14">
         <f ca="1">'Almost Histogram'!B48</f>
-        <v>69.57620562002127</v>
+        <v>65.802601715232484</v>
       </c>
       <c r="C48" s="31">
         <v>0</v>
@@ -17191,7 +17221,7 @@
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="14">
         <f ca="1">'Almost Histogram'!B49</f>
-        <v>65.660848371674192</v>
+        <v>60.686868681992188</v>
       </c>
       <c r="C49" s="31">
         <v>0</v>
@@ -17200,7 +17230,7 @@
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="14">
         <f ca="1">'Almost Histogram'!B50</f>
-        <v>62.368526769562038</v>
+        <v>70.631436966120845</v>
       </c>
       <c r="C50" s="31">
         <v>0</v>
@@ -17209,7 +17239,7 @@
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="14">
         <f ca="1">'Almost Histogram'!B51</f>
-        <v>63.234695801963049</v>
+        <v>67.822231309414491</v>
       </c>
       <c r="C51" s="31">
         <v>0</v>
@@ -17218,7 +17248,7 @@
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="14">
         <f ca="1">'Almost Histogram'!B52</f>
-        <v>69.877266762241959</v>
+        <v>65.451083517140262</v>
       </c>
       <c r="C52" s="31">
         <v>0</v>
@@ -17227,7 +17257,7 @@
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="14">
         <f ca="1">'Almost Histogram'!B53</f>
-        <v>68.614950776555119</v>
+        <v>69.889156638810135</v>
       </c>
       <c r="C53" s="31">
         <v>0</v>
@@ -17236,7 +17266,7 @@
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="14">
         <f ca="1">'Almost Histogram'!B54</f>
-        <v>60.223604529459777</v>
+        <v>62.575792941732757</v>
       </c>
       <c r="C54" s="31">
         <v>0</v>
@@ -17245,7 +17275,7 @@
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="14">
         <f ca="1">'Almost Histogram'!B55</f>
-        <v>70.803936966712754</v>
+        <v>68.790168500099284</v>
       </c>
       <c r="C55" s="31">
         <v>0</v>
@@ -17254,7 +17284,7 @@
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="14">
         <f ca="1">'Almost Histogram'!B56</f>
-        <v>65.406153874396821</v>
+        <v>65.195396415878776</v>
       </c>
       <c r="C56" s="31">
         <v>0</v>
@@ -17263,7 +17293,7 @@
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57" s="14">
         <f ca="1">'Almost Histogram'!B57</f>
-        <v>62.478361733531543</v>
+        <v>67.083526236133267</v>
       </c>
       <c r="C57" s="31">
         <v>0</v>
@@ -17272,7 +17302,7 @@
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="14">
         <f ca="1">'Almost Histogram'!B58</f>
-        <v>65.733687038141014</v>
+        <v>69.226471004443937</v>
       </c>
       <c r="C58" s="31">
         <v>0</v>
@@ -17281,7 +17311,7 @@
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="14">
         <f ca="1">'Almost Histogram'!B59</f>
-        <v>61.344876881641696</v>
+        <v>61.030827750936695</v>
       </c>
       <c r="C59" s="31">
         <v>0</v>
@@ -17290,7 +17320,7 @@
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="14">
         <f ca="1">'Almost Histogram'!B60</f>
-        <v>66.240712540221054</v>
+        <v>63.986155098356939</v>
       </c>
       <c r="C60" s="31">
         <v>0</v>
@@ -17299,7 +17329,7 @@
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="14">
         <f ca="1">'Almost Histogram'!B61</f>
-        <v>64.539003450063646</v>
+        <v>63.699223418430471</v>
       </c>
       <c r="C61" s="31">
         <v>0</v>
@@ -17308,7 +17338,7 @@
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62" s="14">
         <f ca="1">'Almost Histogram'!B62</f>
-        <v>64.106198254993345</v>
+        <v>60.524657455882306</v>
       </c>
       <c r="C62" s="31">
         <v>0</v>
@@ -17317,7 +17347,7 @@
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" s="14">
         <f ca="1">'Almost Histogram'!B63</f>
-        <v>66.309521273648855</v>
+        <v>63.690036126164046</v>
       </c>
       <c r="C63" s="31">
         <v>0</v>
@@ -17326,7 +17356,7 @@
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64" s="14">
         <f ca="1">'Almost Histogram'!B64</f>
-        <v>62.523738128542149</v>
+        <v>68.393102668615157</v>
       </c>
       <c r="C64" s="31">
         <v>0</v>
@@ -17335,7 +17365,7 @@
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" s="14">
         <f ca="1">'Almost Histogram'!B65</f>
-        <v>69.687286369623536</v>
+        <v>72.965816474382478</v>
       </c>
       <c r="C65" s="31">
         <v>0</v>
@@ -17344,7 +17374,7 @@
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" s="14">
         <f ca="1">'Almost Histogram'!B66</f>
-        <v>61.730907352530977</v>
+        <v>69.132891507536783</v>
       </c>
       <c r="C66" s="31">
         <v>0</v>
@@ -17353,7 +17383,7 @@
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67" s="14">
         <f ca="1">'Almost Histogram'!B67</f>
-        <v>61.341755030029134</v>
+        <v>64.560732642842893</v>
       </c>
       <c r="C67" s="31">
         <v>0</v>
@@ -17362,7 +17392,7 @@
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68" s="14">
         <f ca="1">'Almost Histogram'!B68</f>
-        <v>69.65492612657728</v>
+        <v>65.06553956316084</v>
       </c>
       <c r="C68" s="31">
         <v>0</v>
@@ -17371,7 +17401,7 @@
     <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69" s="14">
         <f ca="1">'Almost Histogram'!B69</f>
-        <v>69.561719211726725</v>
+        <v>67.584435173268702</v>
       </c>
       <c r="C69" s="31">
         <v>0</v>
@@ -17380,7 +17410,7 @@
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70" s="14">
         <f ca="1">'Almost Histogram'!B70</f>
-        <v>65.511879244613937</v>
+        <v>63.388505838246573</v>
       </c>
       <c r="C70" s="31">
         <v>0</v>
@@ -17389,7 +17419,7 @@
     <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71" s="14">
         <f ca="1">'Almost Histogram'!B71</f>
-        <v>63.400143040605201</v>
+        <v>68.826396011148987</v>
       </c>
       <c r="C71" s="31">
         <v>0</v>
@@ -17398,7 +17428,7 @@
     <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72" s="14">
         <f ca="1">'Almost Histogram'!B72</f>
-        <v>68.935900027782765</v>
+        <v>66.901953310334136</v>
       </c>
       <c r="C72" s="31">
         <v>0</v>
@@ -17407,7 +17437,7 @@
     <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73" s="14">
         <f ca="1">'Almost Histogram'!B73</f>
-        <v>58.274445673974355</v>
+        <v>66.847864430089132</v>
       </c>
       <c r="C73" s="31">
         <v>0</v>
@@ -17416,7 +17446,7 @@
     <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74" s="14">
         <f ca="1">'Almost Histogram'!B74</f>
-        <v>65.875412947247852</v>
+        <v>63.959480931125611</v>
       </c>
       <c r="C74" s="31">
         <v>0</v>
@@ -17425,7 +17455,7 @@
     <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75" s="14">
         <f ca="1">'Almost Histogram'!B75</f>
-        <v>68.3712034609309</v>
+        <v>67.00248895781742</v>
       </c>
       <c r="C75" s="31">
         <v>0</v>
@@ -17434,7 +17464,7 @@
     <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76" s="14">
         <f ca="1">'Almost Histogram'!B76</f>
-        <v>67.790685459937805</v>
+        <v>61.846276541973559</v>
       </c>
       <c r="C76" s="31">
         <v>0</v>
@@ -17443,7 +17473,7 @@
     <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77" s="14">
         <f ca="1">'Almost Histogram'!B77</f>
-        <v>67.193867540338374</v>
+        <v>68.749918497984808</v>
       </c>
       <c r="C77" s="31">
         <v>0</v>
@@ -17452,7 +17482,7 @@
     <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78" s="14">
         <f ca="1">'Almost Histogram'!B78</f>
-        <v>63.511825680366904</v>
+        <v>67.412689056446894</v>
       </c>
       <c r="C78" s="31">
         <v>0</v>
@@ -17461,7 +17491,7 @@
     <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79" s="14">
         <f ca="1">'Almost Histogram'!B79</f>
-        <v>67.699207332452957</v>
+        <v>68.295978068811891</v>
       </c>
       <c r="C79" s="31">
         <v>0</v>
@@ -17470,7 +17500,7 @@
     <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80" s="14">
         <f ca="1">'Almost Histogram'!B80</f>
-        <v>66.491354103346495</v>
+        <v>63.508756989083238</v>
       </c>
       <c r="C80" s="31">
         <v>0</v>
@@ -17479,7 +17509,7 @@
     <row r="81" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B81" s="14">
         <f ca="1">'Almost Histogram'!B81</f>
-        <v>67.422302083424213</v>
+        <v>61.360217869183117</v>
       </c>
       <c r="C81" s="31">
         <v>0</v>
@@ -17488,7 +17518,7 @@
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B82" s="14">
         <f ca="1">'Almost Histogram'!B82</f>
-        <v>71.851338202611345</v>
+        <v>70.181761015750197</v>
       </c>
       <c r="C82" s="31">
         <v>0</v>
@@ -17497,7 +17527,7 @@
     <row r="83" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B83" s="14">
         <f ca="1">'Almost Histogram'!B83</f>
-        <v>68.52922467858356</v>
+        <v>67.717765900309033</v>
       </c>
       <c r="C83" s="31">
         <v>0</v>
@@ -17506,7 +17536,7 @@
     <row r="84" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B84" s="14">
         <f ca="1">'Almost Histogram'!B84</f>
-        <v>63.337405874236993</v>
+        <v>66.949422645155238</v>
       </c>
       <c r="C84" s="31">
         <v>0</v>
@@ -17515,7 +17545,7 @@
     <row r="85" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B85" s="14">
         <f ca="1">'Almost Histogram'!B85</f>
-        <v>65.34458773689299</v>
+        <v>67.580467316864755</v>
       </c>
       <c r="C85" s="31">
         <v>0</v>
@@ -17524,7 +17554,7 @@
     <row r="86" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B86" s="14">
         <f ca="1">'Almost Histogram'!B86</f>
-        <v>64.235810639210456</v>
+        <v>65.615480189559364</v>
       </c>
       <c r="C86" s="31">
         <v>0</v>
@@ -17533,7 +17563,7 @@
     <row r="87" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B87" s="14">
         <f ca="1">'Almost Histogram'!B87</f>
-        <v>69.085570337652257</v>
+        <v>64.663874146530233</v>
       </c>
       <c r="C87" s="31">
         <v>0</v>
@@ -17542,7 +17572,7 @@
     <row r="88" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B88" s="14">
         <f ca="1">'Almost Histogram'!B88</f>
-        <v>64.501702664742027</v>
+        <v>63.554668904705267</v>
       </c>
       <c r="C88" s="31">
         <v>0</v>
@@ -17551,7 +17581,7 @@
     <row r="89" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B89" s="14">
         <f ca="1">'Almost Histogram'!B89</f>
-        <v>64.023955392929409</v>
+        <v>64.212661108492156</v>
       </c>
       <c r="C89" s="31">
         <v>0</v>
@@ -17560,7 +17590,7 @@
     <row r="90" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B90" s="14">
         <f ca="1">'Almost Histogram'!B90</f>
-        <v>67.78337711608296</v>
+        <v>63.582420345152578</v>
       </c>
       <c r="C90" s="31">
         <v>0</v>
@@ -17569,7 +17599,7 @@
     <row r="91" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B91" s="14">
         <f ca="1">'Almost Histogram'!B91</f>
-        <v>64.917425313046166</v>
+        <v>62.866769667379245</v>
       </c>
       <c r="C91" s="31">
         <v>0</v>
@@ -17578,7 +17608,7 @@
     <row r="92" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B92" s="14">
         <f ca="1">'Almost Histogram'!B92</f>
-        <v>62.31059437379664</v>
+        <v>69.763586669985443</v>
       </c>
       <c r="C92" s="31">
         <v>0</v>
@@ -17587,7 +17617,7 @@
     <row r="93" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B93" s="14">
         <f ca="1">'Almost Histogram'!B93</f>
-        <v>67.029092748141395</v>
+        <v>66.019920085971251</v>
       </c>
       <c r="C93" s="31">
         <v>0</v>
@@ -17596,7 +17626,7 @@
     <row r="94" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B94" s="14">
         <f ca="1">'Almost Histogram'!B94</f>
-        <v>65.152264894695918</v>
+        <v>68.577897562400949</v>
       </c>
       <c r="C94" s="31">
         <v>0</v>
@@ -17605,7 +17635,7 @@
     <row r="95" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B95" s="14">
         <f ca="1">'Almost Histogram'!B95</f>
-        <v>61.199775990691577</v>
+        <v>62.928766757172859</v>
       </c>
       <c r="C95" s="31">
         <v>0</v>
@@ -17614,7 +17644,7 @@
     <row r="96" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B96" s="14">
         <f ca="1">'Almost Histogram'!B96</f>
-        <v>67.262455224716504</v>
+        <v>60.650378600522203</v>
       </c>
       <c r="C96" s="31">
         <v>0</v>
@@ -17623,7 +17653,7 @@
     <row r="97" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B97" s="14">
         <f ca="1">'Almost Histogram'!B97</f>
-        <v>64.354946312367261</v>
+        <v>62.55492046456169</v>
       </c>
       <c r="C97" s="31">
         <v>0</v>
@@ -17632,7 +17662,7 @@
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B98" s="14">
         <f ca="1">'Almost Histogram'!B98</f>
-        <v>63.219410471693351</v>
+        <v>64.339837049717559</v>
       </c>
       <c r="C98" s="31">
         <v>0</v>
@@ -17641,7 +17671,7 @@
     <row r="99" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B99" s="14">
         <f ca="1">'Almost Histogram'!B99</f>
-        <v>65.831785088530282</v>
+        <v>64.601510691071496</v>
       </c>
       <c r="C99" s="31">
         <v>0</v>
@@ -17650,7 +17680,7 @@
     <row r="100" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B100" s="14">
         <f ca="1">'Almost Histogram'!B100</f>
-        <v>66.197320849148809</v>
+        <v>69.18219008879332</v>
       </c>
       <c r="C100" s="31">
         <v>0</v>
@@ -17659,7 +17689,7 @@
     <row r="101" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B101" s="14">
         <f ca="1">'Almost Histogram'!B101</f>
-        <v>62.884291193572345</v>
+        <v>65.18081678544219</v>
       </c>
       <c r="C101" s="31">
         <v>0</v>
@@ -17668,7 +17698,7 @@
     <row r="102" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B102" s="14">
         <f ca="1">'Almost Histogram'!B102</f>
-        <v>63.460679233636078</v>
+        <v>62.53000958906641</v>
       </c>
       <c r="C102" s="31">
         <v>0</v>
@@ -17677,7 +17707,7 @@
     <row r="103" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B103" s="14">
         <f ca="1">'Almost Histogram'!B103</f>
-        <v>73.396319499285866</v>
+        <v>67.023429216239364</v>
       </c>
       <c r="C103" s="31">
         <v>0</v>
@@ -17686,7 +17716,7 @@
     <row r="104" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B104" s="14">
         <f ca="1">'Almost Histogram'!B104</f>
-        <v>69.092637651587808</v>
+        <v>65.419694574125401</v>
       </c>
       <c r="C104" s="31">
         <v>0</v>
@@ -17695,7 +17725,7 @@
     <row r="105" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B105" s="14">
         <f ca="1">'Almost Histogram'!B105</f>
-        <v>64.589616250500043</v>
+        <v>64.527943122945032</v>
       </c>
       <c r="C105" s="31">
         <v>0</v>
@@ -17704,7 +17734,7 @@
     <row r="106" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B106" s="14">
         <f ca="1">'Almost Histogram'!B106</f>
-        <v>68.946282091601773</v>
+        <v>63.990051817670349</v>
       </c>
       <c r="C106" s="31">
         <v>0</v>
@@ -17713,7 +17743,7 @@
     <row r="107" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B107" s="14">
         <f ca="1">'Almost Histogram'!B107</f>
-        <v>65.383162698307871</v>
+        <v>64.048047928929293</v>
       </c>
       <c r="C107" s="31">
         <v>0</v>
@@ -17722,7 +17752,7 @@
     <row r="108" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B108" s="14">
         <f ca="1">'Almost Histogram'!B108</f>
-        <v>70.301066217215109</v>
+        <v>66.004054158487477</v>
       </c>
       <c r="C108" s="31">
         <v>0</v>
@@ -17731,7 +17761,7 @@
     <row r="109" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B109" s="14">
         <f ca="1">'Almost Histogram'!B109</f>
-        <v>70.203168423284751</v>
+        <v>63.730839164069721</v>
       </c>
       <c r="C109" s="31">
         <v>0</v>
@@ -17740,7 +17770,7 @@
     <row r="110" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B110" s="14">
         <f ca="1">'Almost Histogram'!B110</f>
-        <v>71.809462331261898</v>
+        <v>64.306882565104132</v>
       </c>
       <c r="C110" s="31">
         <v>0</v>
@@ -17749,7 +17779,7 @@
     <row r="111" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B111" s="14">
         <f ca="1">'Almost Histogram'!B111</f>
-        <v>73.447719531860685</v>
+        <v>65.939897352211545</v>
       </c>
       <c r="C111" s="31">
         <v>0</v>
@@ -17758,7 +17788,7 @@
     <row r="112" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B112" s="14">
         <f ca="1">'Almost Histogram'!B112</f>
-        <v>68.717819107289174</v>
+        <v>64.462662881571831</v>
       </c>
       <c r="C112" s="31">
         <v>0</v>
@@ -17767,7 +17797,7 @@
     <row r="113" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B113" s="14">
         <f ca="1">'Almost Histogram'!B113</f>
-        <v>72.504274540477724</v>
+        <v>68.607508675355433</v>
       </c>
       <c r="C113" s="31">
         <v>0</v>
@@ -17776,7 +17806,7 @@
     <row r="114" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B114" s="14">
         <f ca="1">'Almost Histogram'!B114</f>
-        <v>69.951422067288604</v>
+        <v>64.862267423302882</v>
       </c>
       <c r="C114" s="31">
         <v>0</v>
@@ -17785,7 +17815,7 @@
     <row r="115" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B115" s="14">
         <f ca="1">'Almost Histogram'!B115</f>
-        <v>58.303169578667131</v>
+        <v>65.029873080459183</v>
       </c>
       <c r="C115" s="31">
         <v>0</v>
@@ -17794,7 +17824,7 @@
     <row r="116" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B116" s="14">
         <f ca="1">'Almost Histogram'!B116</f>
-        <v>66.480416186446703</v>
+        <v>60.474622861672934</v>
       </c>
       <c r="C116" s="31">
         <v>0</v>
@@ -17803,7 +17833,7 @@
     <row r="117" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B117" s="14">
         <f ca="1">'Almost Histogram'!B117</f>
-        <v>68.577242095825738</v>
+        <v>66.903253566519751</v>
       </c>
       <c r="C117" s="31">
         <v>0</v>
@@ -17812,7 +17842,7 @@
     <row r="118" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B118" s="14">
         <f ca="1">'Almost Histogram'!B118</f>
-        <v>65.552419774222798</v>
+        <v>61.708456177973119</v>
       </c>
       <c r="C118" s="31">
         <v>0</v>
@@ -17821,7 +17851,7 @@
     <row r="119" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B119" s="14">
         <f ca="1">'Almost Histogram'!B119</f>
-        <v>63.471827882930448</v>
+        <v>64.37725790007093</v>
       </c>
       <c r="C119" s="31">
         <v>0</v>
@@ -17830,7 +17860,7 @@
     <row r="120" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B120" s="14">
         <f ca="1">'Almost Histogram'!B120</f>
-        <v>63.740992429480627</v>
+        <v>68.591284302048706</v>
       </c>
       <c r="C120" s="31">
         <v>0</v>
@@ -17839,7 +17869,7 @@
     <row r="121" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B121" s="14">
         <f ca="1">'Almost Histogram'!B121</f>
-        <v>61.109774491819493</v>
+        <v>70.403276438005832</v>
       </c>
       <c r="C121" s="31">
         <v>0</v>
@@ -17848,7 +17878,7 @@
     <row r="122" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B122" s="14">
         <f ca="1">'Almost Histogram'!B122</f>
-        <v>71.67991871011391</v>
+        <v>62.94308564332897</v>
       </c>
       <c r="C122" s="31">
         <v>0</v>
@@ -17857,7 +17887,7 @@
     <row r="123" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B123" s="14">
         <f ca="1">'Almost Histogram'!B123</f>
-        <v>68.559326478881999</v>
+        <v>65.928881334843581</v>
       </c>
       <c r="C123" s="31">
         <v>0</v>
@@ -17866,7 +17896,7 @@
     <row r="124" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B124" s="14">
         <f ca="1">'Almost Histogram'!B124</f>
-        <v>71.443183406472144</v>
+        <v>62.630583080097253</v>
       </c>
       <c r="C124" s="31">
         <v>0</v>
